--- a/research/traditional_assets/database/data/morocco/morocco_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/morocco/morocco_real_estate_general_diversified.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08623518464334165</v>
+        <v>0.08598983205248296</v>
       </c>
       <c r="C2">
-        <v>1219.683386557321</v>
+        <v>1214.69060165957</v>
       </c>
       <c r="D2">
-        <v>1199.083386557321</v>
+        <v>1206.40360165957</v>
       </c>
       <c r="E2">
-        <v>-185.5</v>
+        <v>-173.187</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>12.313</v>
       </c>
       <c r="G2">
         <v>20.6</v>
@@ -1582,28 +1582,28 @@
         <v>33.17</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6193438999999999</v>
       </c>
       <c r="N2">
-        <v>33.17</v>
+        <v>32.5506561</v>
       </c>
       <c r="O2">
-        <v>10.6144</v>
+        <v>10.416209952</v>
       </c>
       <c r="P2">
-        <v>22.5556</v>
+        <v>22.134446148</v>
       </c>
       <c r="Q2">
-        <v>28.2856</v>
+        <v>27.864446148</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08623518464334165</v>
+        <v>0.08651292126513431</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5306258460701789</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>53.55667505565165</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08598983205248296</v>
+        <v>0.08574447946162428</v>
       </c>
       <c r="C3">
-        <v>1214.69060165957</v>
+        <v>1209.787743268069</v>
       </c>
       <c r="D3">
-        <v>1206.40360165957</v>
+        <v>1213.813743268069</v>
       </c>
       <c r="E3">
-        <v>-173.187</v>
+        <v>-160.874</v>
       </c>
       <c r="F3">
-        <v>12.313</v>
+        <v>24.626</v>
       </c>
       <c r="G3">
         <v>20.6</v>
@@ -1664,28 +1664,28 @@
         <v>33.17</v>
       </c>
       <c r="M3">
-        <v>0.6193438999999999</v>
+        <v>1.2386878</v>
       </c>
       <c r="N3">
-        <v>32.5506561</v>
+        <v>31.9313122</v>
       </c>
       <c r="O3">
-        <v>10.416209952</v>
+        <v>10.218019904</v>
       </c>
       <c r="P3">
-        <v>22.134446148</v>
+        <v>21.713292296</v>
       </c>
       <c r="Q3">
-        <v>27.864446148</v>
+        <v>27.443292296</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08651292126513431</v>
+        <v>0.08679632598124926</v>
       </c>
       <c r="T3">
-        <v>0.5306258460701789</v>
+        <v>0.5343195595792007</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>53.55667505565165</v>
+        <v>26.77833752782582</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08574447946162428</v>
+        <v>0.08549912687076558</v>
       </c>
       <c r="C4">
-        <v>1209.787743268069</v>
+        <v>1204.976478701702</v>
       </c>
       <c r="D4">
-        <v>1213.813743268069</v>
+        <v>1221.315478701702</v>
       </c>
       <c r="E4">
-        <v>-160.874</v>
+        <v>-148.561</v>
       </c>
       <c r="F4">
-        <v>24.626</v>
+        <v>36.939</v>
       </c>
       <c r="G4">
         <v>20.6</v>
@@ -1746,28 +1746,28 @@
         <v>33.17</v>
       </c>
       <c r="M4">
-        <v>1.2386878</v>
+        <v>1.8580317</v>
       </c>
       <c r="N4">
-        <v>31.9313122</v>
+        <v>31.3119683</v>
       </c>
       <c r="O4">
-        <v>10.218019904</v>
+        <v>10.019829856</v>
       </c>
       <c r="P4">
-        <v>21.713292296</v>
+        <v>21.292138444</v>
       </c>
       <c r="Q4">
-        <v>27.443292296</v>
+        <v>27.022138444</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08679632598124926</v>
+        <v>0.08708557409357276</v>
       </c>
       <c r="T4">
-        <v>0.5343195595792007</v>
+        <v>0.5380894321296459</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>26.77833752782582</v>
+        <v>17.85222501855054</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08549912687076558</v>
+        <v>0.08525377427990688</v>
       </c>
       <c r="C5">
-        <v>1204.976478701702</v>
+        <v>1200.258516753813</v>
       </c>
       <c r="D5">
-        <v>1221.315478701702</v>
+        <v>1228.910516753813</v>
       </c>
       <c r="E5">
-        <v>-148.561</v>
+        <v>-136.248</v>
       </c>
       <c r="F5">
-        <v>36.939</v>
+        <v>49.252</v>
       </c>
       <c r="G5">
         <v>20.6</v>
@@ -1828,28 +1828,28 @@
         <v>33.17</v>
       </c>
       <c r="M5">
-        <v>1.8580317</v>
+        <v>2.4773756</v>
       </c>
       <c r="N5">
-        <v>31.3119683</v>
+        <v>30.6926244</v>
       </c>
       <c r="O5">
-        <v>10.019829856</v>
+        <v>9.821639808</v>
       </c>
       <c r="P5">
-        <v>21.292138444</v>
+        <v>20.870984592</v>
       </c>
       <c r="Q5">
-        <v>27.022138444</v>
+        <v>26.600984592</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08708557409357276</v>
+        <v>0.08738084820823634</v>
       </c>
       <c r="T5">
-        <v>0.5380894321296459</v>
+        <v>0.5419378436915586</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>17.85222501855054</v>
+        <v>13.38916876391291</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08525377427990688</v>
+        <v>0.08505942168904819</v>
       </c>
       <c r="C6">
-        <v>1200.258516753813</v>
+        <v>1194.029201448823</v>
       </c>
       <c r="D6">
-        <v>1228.910516753813</v>
+        <v>1234.994201448823</v>
       </c>
       <c r="E6">
-        <v>-136.248</v>
+        <v>-123.935</v>
       </c>
       <c r="F6">
-        <v>49.252</v>
+        <v>61.565</v>
       </c>
       <c r="G6">
         <v>20.6</v>
@@ -1910,45 +1910,45 @@
         <v>33.17</v>
       </c>
       <c r="M6">
-        <v>2.4773756</v>
+        <v>3.189067</v>
       </c>
       <c r="N6">
-        <v>30.6926244</v>
+        <v>29.980933</v>
       </c>
       <c r="O6">
-        <v>9.821639808</v>
+        <v>9.59389856</v>
       </c>
       <c r="P6">
-        <v>20.870984592</v>
+        <v>20.38703444</v>
       </c>
       <c r="Q6">
-        <v>26.600984592</v>
+        <v>26.11703444</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08738084820823634</v>
+        <v>0.08768233862005073</v>
       </c>
       <c r="T6">
-        <v>0.5419378436915586</v>
+        <v>0.5458672744442484</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.32</v>
       </c>
       <c r="W6">
-        <v>0.034204</v>
+        <v>0.035224</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>13.38916876391291</v>
+        <v>10.40116121737173</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08505942168904819</v>
+        <v>0.0848936290981895</v>
       </c>
       <c r="C7">
-        <v>1194.029201448823</v>
+        <v>1186.95370160107</v>
       </c>
       <c r="D7">
-        <v>1234.994201448823</v>
+        <v>1240.23170160107</v>
       </c>
       <c r="E7">
-        <v>-123.935</v>
+        <v>-111.622</v>
       </c>
       <c r="F7">
-        <v>61.565</v>
+        <v>73.878</v>
       </c>
       <c r="G7">
         <v>20.6</v>
@@ -1992,45 +1992,45 @@
         <v>33.17</v>
       </c>
       <c r="M7">
-        <v>3.189067</v>
+        <v>3.952473</v>
       </c>
       <c r="N7">
-        <v>29.980933</v>
+        <v>29.217527</v>
       </c>
       <c r="O7">
-        <v>9.59389856</v>
+        <v>9.34960864</v>
       </c>
       <c r="P7">
-        <v>20.38703444</v>
+        <v>19.86791836</v>
       </c>
       <c r="Q7">
-        <v>26.11703444</v>
+        <v>25.59791836</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08768233862005073</v>
+        <v>0.08799024372147819</v>
       </c>
       <c r="T7">
-        <v>0.5458672744442484</v>
+        <v>0.5498803101065699</v>
       </c>
       <c r="U7">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V7">
         <v>0.32</v>
       </c>
       <c r="W7">
-        <v>0.035224</v>
+        <v>0.03638</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y7">
-        <v>10.40116121737173</v>
+        <v>8.392214190963481</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0848936290981895</v>
+        <v>0.08470811650733082</v>
       </c>
       <c r="C8">
-        <v>1186.95370160107</v>
+        <v>1180.554084639947</v>
       </c>
       <c r="D8">
-        <v>1240.23170160107</v>
+        <v>1246.145084639947</v>
       </c>
       <c r="E8">
-        <v>-111.622</v>
+        <v>-99.30900000000001</v>
       </c>
       <c r="F8">
-        <v>73.878</v>
+        <v>86.19099999999999</v>
       </c>
       <c r="G8">
         <v>20.6</v>
@@ -2074,45 +2074,45 @@
         <v>33.17</v>
       </c>
       <c r="M8">
-        <v>3.952473</v>
+        <v>4.6801713</v>
       </c>
       <c r="N8">
-        <v>29.217527</v>
+        <v>28.4898287</v>
       </c>
       <c r="O8">
-        <v>9.34960864</v>
+        <v>9.116745184000001</v>
       </c>
       <c r="P8">
-        <v>19.86791836</v>
+        <v>19.373083516</v>
       </c>
       <c r="Q8">
-        <v>25.59791836</v>
+        <v>25.103083516</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08799024372147819</v>
+        <v>0.08830477043799012</v>
       </c>
       <c r="T8">
-        <v>0.5498803101065699</v>
+        <v>0.5539796476110919</v>
       </c>
       <c r="U8">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V8">
         <v>0.32</v>
       </c>
       <c r="W8">
-        <v>0.03638</v>
+        <v>0.036924</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y8">
-        <v>8.392214190963481</v>
+        <v>7.087347422518489</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08470811650733082</v>
+        <v>0.08448996391647212</v>
       </c>
       <c r="C9">
-        <v>1180.554084639947</v>
+        <v>1175.267448877115</v>
       </c>
       <c r="D9">
-        <v>1246.145084639947</v>
+        <v>1253.171448877115</v>
       </c>
       <c r="E9">
-        <v>-99.309</v>
+        <v>-86.996</v>
       </c>
       <c r="F9">
-        <v>86.191</v>
+        <v>98.504</v>
       </c>
       <c r="G9">
         <v>20.6</v>
@@ -2156,28 +2156,28 @@
         <v>33.17</v>
       </c>
       <c r="M9">
-        <v>4.6801713</v>
+        <v>5.3487672</v>
       </c>
       <c r="N9">
-        <v>28.4898287</v>
+        <v>27.8212328</v>
       </c>
       <c r="O9">
-        <v>9.116745184000001</v>
+        <v>8.902794496</v>
       </c>
       <c r="P9">
-        <v>19.373083516</v>
+        <v>18.918438304</v>
       </c>
       <c r="Q9">
-        <v>25.103083516</v>
+        <v>24.648438304</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08830477043799012</v>
+        <v>0.08862613469181752</v>
       </c>
       <c r="T9">
-        <v>0.5539796476110919</v>
+        <v>0.5581681011483208</v>
       </c>
       <c r="U9">
         <v>0.0543</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>7.087347422518487</v>
+        <v>6.201428994703677</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08448996391647212</v>
+        <v>0.08433301132561342</v>
       </c>
       <c r="C10">
-        <v>1175.267448877115</v>
+        <v>1168.058864517755</v>
       </c>
       <c r="D10">
-        <v>1253.171448877115</v>
+        <v>1258.275864517755</v>
       </c>
       <c r="E10">
-        <v>-86.996</v>
+        <v>-74.68300000000001</v>
       </c>
       <c r="F10">
-        <v>98.504</v>
+        <v>110.817</v>
       </c>
       <c r="G10">
         <v>20.6</v>
@@ -2238,45 +2238,45 @@
         <v>33.17</v>
       </c>
       <c r="M10">
-        <v>5.3487672</v>
+        <v>6.1281801</v>
       </c>
       <c r="N10">
-        <v>27.8212328</v>
+        <v>27.0418199</v>
       </c>
       <c r="O10">
-        <v>8.902794496</v>
+        <v>8.653382368000001</v>
       </c>
       <c r="P10">
-        <v>18.918438304</v>
+        <v>18.388437532</v>
       </c>
       <c r="Q10">
-        <v>24.648438304</v>
+        <v>24.118437532</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08862613469181752</v>
+        <v>0.08895456189627848</v>
       </c>
       <c r="T10">
-        <v>0.5581681011483208</v>
+        <v>0.5624486086094449</v>
       </c>
       <c r="U10">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V10">
         <v>0.32</v>
       </c>
       <c r="W10">
-        <v>0.036924</v>
+        <v>0.037604</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>6.201428994703677</v>
+        <v>5.412699930277832</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08433301132561342</v>
+        <v>0.08412165873475473</v>
       </c>
       <c r="C11">
-        <v>1168.058864517755</v>
+        <v>1162.685539697827</v>
       </c>
       <c r="D11">
-        <v>1258.275864517755</v>
+        <v>1265.215539697827</v>
       </c>
       <c r="E11">
-        <v>-74.68300000000001</v>
+        <v>-62.37000000000002</v>
       </c>
       <c r="F11">
-        <v>110.817</v>
+        <v>123.13</v>
       </c>
       <c r="G11">
         <v>20.6</v>
@@ -2320,28 +2320,28 @@
         <v>33.17</v>
       </c>
       <c r="M11">
-        <v>6.1281801</v>
+        <v>6.809088999999999</v>
       </c>
       <c r="N11">
-        <v>27.0418199</v>
+        <v>26.360911</v>
       </c>
       <c r="O11">
-        <v>8.653382368000001</v>
+        <v>8.435491520000001</v>
       </c>
       <c r="P11">
-        <v>18.388437532</v>
+        <v>17.92541948</v>
       </c>
       <c r="Q11">
-        <v>24.118437532</v>
+        <v>23.65541948</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08895456189627848</v>
+        <v>0.08929028748306081</v>
       </c>
       <c r="T11">
-        <v>0.5624486086094449</v>
+        <v>0.566824238458594</v>
       </c>
       <c r="U11">
         <v>0.0553</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>5.412699930277832</v>
+        <v>4.871429937250049</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08412165873475473</v>
+        <v>0.08409730614389603</v>
       </c>
       <c r="C12">
-        <v>1162.685539697827</v>
+        <v>1151.177068253193</v>
       </c>
       <c r="D12">
-        <v>1265.215539697827</v>
+        <v>1266.020068253193</v>
       </c>
       <c r="E12">
-        <v>-62.37</v>
+        <v>-50.05700000000002</v>
       </c>
       <c r="F12">
-        <v>123.13</v>
+        <v>135.443</v>
       </c>
       <c r="G12">
         <v>20.6</v>
@@ -2402,45 +2402,45 @@
         <v>33.17</v>
       </c>
       <c r="M12">
-        <v>6.809089</v>
+        <v>7.8286054</v>
       </c>
       <c r="N12">
-        <v>26.360911</v>
+        <v>25.3413946</v>
       </c>
       <c r="O12">
-        <v>8.435491520000001</v>
+        <v>8.109246272</v>
       </c>
       <c r="P12">
-        <v>17.92541948</v>
+        <v>17.232148328</v>
       </c>
       <c r="Q12">
-        <v>23.65541948</v>
+        <v>22.962148328</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08929028748306081</v>
+        <v>0.08963355746505172</v>
       </c>
       <c r="T12">
-        <v>0.566824238458594</v>
+        <v>0.571298197068398</v>
       </c>
       <c r="U12">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V12">
         <v>0.32</v>
       </c>
       <c r="W12">
-        <v>0.037604</v>
+        <v>0.039304</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.871429937250049</v>
+        <v>4.237025409404337</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08409730614389603</v>
+        <v>0.08418855355303735</v>
       </c>
       <c r="C13">
-        <v>1151.177068253193</v>
+        <v>1135.854810532934</v>
       </c>
       <c r="D13">
-        <v>1266.020068253193</v>
+        <v>1263.010810532935</v>
       </c>
       <c r="E13">
-        <v>-50.05700000000002</v>
+        <v>-37.744</v>
       </c>
       <c r="F13">
-        <v>135.443</v>
+        <v>147.756</v>
       </c>
       <c r="G13">
         <v>20.6</v>
@@ -2484,45 +2484,45 @@
         <v>33.17</v>
       </c>
       <c r="M13">
-        <v>7.8286054</v>
+        <v>9.0574428</v>
       </c>
       <c r="N13">
-        <v>25.3413946</v>
+        <v>24.1125572</v>
       </c>
       <c r="O13">
-        <v>8.109246272</v>
+        <v>7.716018304</v>
       </c>
       <c r="P13">
-        <v>17.232148328</v>
+        <v>16.396538896</v>
       </c>
       <c r="Q13">
-        <v>22.962148328</v>
+        <v>22.126538896</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08963355746505172</v>
+        <v>0.08998462903754244</v>
       </c>
       <c r="T13">
-        <v>0.571298197068398</v>
+        <v>0.5758738365556978</v>
       </c>
       <c r="U13">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V13">
         <v>0.32</v>
       </c>
       <c r="W13">
-        <v>0.039304</v>
+        <v>0.041684</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>4.237025409404337</v>
+        <v>3.662181559678191</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08418855355303735</v>
+        <v>0.08426552096217864</v>
       </c>
       <c r="C14">
-        <v>1135.854810532934</v>
+        <v>1121.014594798621</v>
       </c>
       <c r="D14">
-        <v>1263.010810532935</v>
+        <v>1260.483594798621</v>
       </c>
       <c r="E14">
-        <v>-37.744</v>
+        <v>-25.43100000000001</v>
       </c>
       <c r="F14">
-        <v>147.756</v>
+        <v>160.069</v>
       </c>
       <c r="G14">
         <v>20.6</v>
@@ -2566,45 +2566,45 @@
         <v>33.17</v>
       </c>
       <c r="M14">
-        <v>9.0574428</v>
+        <v>10.2604229</v>
       </c>
       <c r="N14">
-        <v>24.1125572</v>
+        <v>22.9095771</v>
       </c>
       <c r="O14">
-        <v>7.716018304</v>
+        <v>7.331064672</v>
       </c>
       <c r="P14">
-        <v>16.396538896</v>
+        <v>15.578512428</v>
       </c>
       <c r="Q14">
-        <v>22.126538896</v>
+        <v>21.308512428</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08998462903754244</v>
+        <v>0.09034377122089499</v>
       </c>
       <c r="T14">
-        <v>0.5758738365556978</v>
+        <v>0.5805546631576479</v>
       </c>
       <c r="U14">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V14">
         <v>0.32</v>
       </c>
       <c r="W14">
-        <v>0.041684</v>
+        <v>0.043588</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.662181559678191</v>
+        <v>3.232810218767884</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08426552096217864</v>
+        <v>0.08411400837131995</v>
       </c>
       <c r="C15">
-        <v>1121.014594798621</v>
+        <v>1113.686172066861</v>
       </c>
       <c r="D15">
-        <v>1260.483594798621</v>
+        <v>1265.468172066861</v>
       </c>
       <c r="E15">
-        <v>-25.43100000000001</v>
+        <v>-13.11799999999999</v>
       </c>
       <c r="F15">
-        <v>160.069</v>
+        <v>172.382</v>
       </c>
       <c r="G15">
         <v>20.6</v>
@@ -2648,28 +2648,28 @@
         <v>33.17</v>
       </c>
       <c r="M15">
-        <v>10.2604229</v>
+        <v>11.0496862</v>
       </c>
       <c r="N15">
-        <v>22.9095771</v>
+        <v>22.1203138</v>
       </c>
       <c r="O15">
-        <v>7.331064672</v>
+        <v>7.078500416</v>
       </c>
       <c r="P15">
-        <v>15.578512428</v>
+        <v>15.041813384</v>
       </c>
       <c r="Q15">
-        <v>21.308512428</v>
+        <v>20.771813384</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09034377122089499</v>
+        <v>0.09071126554804645</v>
       </c>
       <c r="T15">
-        <v>0.5805546631576479</v>
+        <v>0.5853443461922017</v>
       </c>
       <c r="U15">
         <v>0.0641</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>3.232810218767884</v>
+        <v>3.001895203141606</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08411400837131995</v>
+        <v>0.08515589578046127</v>
       </c>
       <c r="C16">
-        <v>1113.686172066861</v>
+        <v>1067.871829282024</v>
       </c>
       <c r="D16">
-        <v>1265.468172066861</v>
+        <v>1231.966829282024</v>
       </c>
       <c r="E16">
-        <v>-13.11799999999999</v>
+        <v>-0.8049999999999784</v>
       </c>
       <c r="F16">
-        <v>172.382</v>
+        <v>184.695</v>
       </c>
       <c r="G16">
         <v>20.6</v>
@@ -2730,45 +2730,45 @@
         <v>33.17</v>
       </c>
       <c r="M16">
-        <v>11.0496862</v>
+        <v>13.999881</v>
       </c>
       <c r="N16">
-        <v>22.1203138</v>
+        <v>19.170119</v>
       </c>
       <c r="O16">
-        <v>7.078500416</v>
+        <v>6.13443808</v>
       </c>
       <c r="P16">
-        <v>15.041813384</v>
+        <v>13.03568092</v>
       </c>
       <c r="Q16">
-        <v>20.771813384</v>
+        <v>18.76568092</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09071126554804645</v>
+        <v>0.09108740680054267</v>
       </c>
       <c r="T16">
-        <v>0.5853443461922017</v>
+        <v>0.5902467276510979</v>
       </c>
       <c r="U16">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V16">
         <v>0.32</v>
       </c>
       <c r="W16">
-        <v>0.043588</v>
+        <v>0.051544</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.001895203141606</v>
+        <v>2.369305853385468</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08515589578046127</v>
+        <v>0.08508394318960256</v>
       </c>
       <c r="C17">
-        <v>1067.871829282024</v>
+        <v>1057.815303505882</v>
       </c>
       <c r="D17">
-        <v>1231.966829282024</v>
+        <v>1234.223303505882</v>
       </c>
       <c r="E17">
-        <v>-0.8050000000000068</v>
+        <v>11.50800000000001</v>
       </c>
       <c r="F17">
-        <v>184.695</v>
+        <v>197.008</v>
       </c>
       <c r="G17">
         <v>20.6</v>
@@ -2812,28 +2812,28 @@
         <v>33.17</v>
       </c>
       <c r="M17">
-        <v>13.999881</v>
+        <v>14.9332064</v>
       </c>
       <c r="N17">
-        <v>19.170119</v>
+        <v>18.2367936</v>
       </c>
       <c r="O17">
-        <v>6.13443808</v>
+        <v>5.835773951999999</v>
       </c>
       <c r="P17">
-        <v>13.03568092</v>
+        <v>12.401019648</v>
       </c>
       <c r="Q17">
-        <v>18.76568092</v>
+        <v>18.131019648</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09108740680054267</v>
+        <v>0.09147250379714592</v>
       </c>
       <c r="T17">
-        <v>0.5902467276510979</v>
+        <v>0.595265832478063</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.369305853385468</v>
+        <v>2.221224237548876</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08508394318960256</v>
+        <v>0.08501199059874387</v>
       </c>
       <c r="C18">
-        <v>1057.815303505882</v>
+        <v>1047.767058827645</v>
       </c>
       <c r="D18">
-        <v>1234.223303505882</v>
+        <v>1236.488058827645</v>
       </c>
       <c r="E18">
-        <v>11.50800000000001</v>
+        <v>23.821</v>
       </c>
       <c r="F18">
-        <v>197.008</v>
+        <v>209.321</v>
       </c>
       <c r="G18">
         <v>20.6</v>
@@ -2894,28 +2894,28 @@
         <v>33.17</v>
       </c>
       <c r="M18">
-        <v>14.9332064</v>
+        <v>15.8665318</v>
       </c>
       <c r="N18">
-        <v>18.2367936</v>
+        <v>17.3034682</v>
       </c>
       <c r="O18">
-        <v>5.835773951999999</v>
+        <v>5.537109824000001</v>
       </c>
       <c r="P18">
-        <v>12.401019648</v>
+        <v>11.766358376</v>
       </c>
       <c r="Q18">
-        <v>18.131019648</v>
+        <v>17.496358376</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09147250379714592</v>
+        <v>0.09186688023945044</v>
       </c>
       <c r="T18">
-        <v>0.595265832478063</v>
+        <v>0.6004058795900152</v>
       </c>
       <c r="U18">
         <v>0.07580000000000001</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>2.221224237548876</v>
+        <v>2.090563988281295</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08501199059874387</v>
+        <v>0.08667811800788518</v>
       </c>
       <c r="C19">
-        <v>1047.767058827645</v>
+        <v>985.056762027159</v>
       </c>
       <c r="D19">
-        <v>1236.488058827645</v>
+        <v>1186.090762027159</v>
       </c>
       <c r="E19">
-        <v>23.821</v>
+        <v>36.13400000000001</v>
       </c>
       <c r="F19">
-        <v>209.321</v>
+        <v>221.634</v>
       </c>
       <c r="G19">
         <v>20.6</v>
@@ -2976,45 +2976,45 @@
         <v>33.17</v>
       </c>
       <c r="M19">
-        <v>15.8665318</v>
+        <v>19.94706</v>
       </c>
       <c r="N19">
-        <v>17.3034682</v>
+        <v>13.22294</v>
       </c>
       <c r="O19">
-        <v>5.537109824000001</v>
+        <v>4.231340800000001</v>
       </c>
       <c r="P19">
-        <v>11.766358376</v>
+        <v>8.9915992</v>
       </c>
       <c r="Q19">
-        <v>17.496358376</v>
+        <v>14.7215992</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09186688023945044</v>
+        <v>0.09227087561937217</v>
       </c>
       <c r="T19">
-        <v>0.6004058795900152</v>
+        <v>0.605671293704698</v>
       </c>
       <c r="U19">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V19">
         <v>0.32</v>
       </c>
       <c r="W19">
-        <v>0.051544</v>
+        <v>0.06119999999999999</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.090563988281295</v>
+        <v>1.662901700802023</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08667811800788518</v>
+        <v>0.08670272541702649</v>
       </c>
       <c r="C20">
-        <v>985.056762027159</v>
+        <v>972.0302002690522</v>
       </c>
       <c r="D20">
-        <v>1186.090762027159</v>
+        <v>1185.377200269052</v>
       </c>
       <c r="E20">
-        <v>36.13399999999999</v>
+        <v>48.447</v>
       </c>
       <c r="F20">
-        <v>221.634</v>
+        <v>233.947</v>
       </c>
       <c r="G20">
         <v>20.6</v>
@@ -3058,28 +3058,28 @@
         <v>33.17</v>
       </c>
       <c r="M20">
-        <v>19.94706</v>
+        <v>21.05523</v>
       </c>
       <c r="N20">
-        <v>13.22294</v>
+        <v>12.11477</v>
       </c>
       <c r="O20">
-        <v>4.231340800000002</v>
+        <v>3.876726400000001</v>
       </c>
       <c r="P20">
-        <v>8.991599200000003</v>
+        <v>8.238043600000003</v>
       </c>
       <c r="Q20">
-        <v>14.7215992</v>
+        <v>13.9680436</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09227087561937217</v>
+        <v>0.09268484619385986</v>
       </c>
       <c r="T20">
-        <v>0.605671293704698</v>
+        <v>0.6110667180444347</v>
       </c>
       <c r="U20">
         <v>0.09</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>1.662901700802023</v>
+        <v>1.575380558654548</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08670272541702649</v>
+        <v>0.09544024174788013</v>
       </c>
       <c r="C21">
-        <v>972.0302002690522</v>
+        <v>751.0709028119148</v>
       </c>
       <c r="D21">
-        <v>1185.377200269052</v>
+        <v>976.7309028119148</v>
       </c>
       <c r="E21">
-        <v>48.447</v>
+        <v>60.75999999999999</v>
       </c>
       <c r="F21">
-        <v>233.947</v>
+        <v>246.26</v>
       </c>
       <c r="G21">
         <v>20.6</v>
@@ -3140,45 +3140,45 @@
         <v>33.17</v>
       </c>
       <c r="M21">
-        <v>21.05523</v>
+        <v>36.150968</v>
       </c>
       <c r="N21">
-        <v>12.11477</v>
+        <v>-2.980967999999997</v>
       </c>
       <c r="O21">
-        <v>3.876726400000001</v>
+        <v>-0.9539097599999992</v>
       </c>
       <c r="P21">
-        <v>8.238043600000003</v>
+        <v>-2.027058239999998</v>
       </c>
       <c r="Q21">
-        <v>13.9680436</v>
+        <v>3.702941760000003</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09268484619385986</v>
+        <v>0.09337590520604727</v>
       </c>
       <c r="T21">
-        <v>0.6110667180444347</v>
+        <v>0.6200735336113734</v>
       </c>
       <c r="U21">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.32</v>
+        <v>0.2936131613405207</v>
       </c>
       <c r="W21">
-        <v>0.06119999999999999</v>
+        <v>0.1036975879152116</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y21">
-        <v>1.575380558654548</v>
+        <v>0.9175411291891272</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09544024174788013</v>
+        <v>0.09645024174788012</v>
       </c>
       <c r="C22">
-        <v>751.0709028119148</v>
+        <v>719.2812294970965</v>
       </c>
       <c r="D22">
-        <v>976.7309028119148</v>
+        <v>957.2542294970966</v>
       </c>
       <c r="E22">
-        <v>60.75999999999999</v>
+        <v>73.07300000000004</v>
       </c>
       <c r="F22">
-        <v>246.26</v>
+        <v>258.573</v>
       </c>
       <c r="G22">
         <v>20.6</v>
@@ -3222,37 +3222,37 @@
         <v>33.17</v>
       </c>
       <c r="M22">
-        <v>36.150968</v>
+        <v>37.95851640000001</v>
       </c>
       <c r="N22">
-        <v>-2.980967999999997</v>
+        <v>-4.788516400000006</v>
       </c>
       <c r="O22">
-        <v>-0.9539097599999992</v>
+        <v>-1.532325248000002</v>
       </c>
       <c r="P22">
-        <v>-2.027058239999998</v>
+        <v>-3.256191152000004</v>
       </c>
       <c r="Q22">
-        <v>3.702941760000003</v>
+        <v>2.473808847999996</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09337590520604727</v>
+        <v>0.09397813185422507</v>
       </c>
       <c r="T22">
-        <v>0.6200735336113734</v>
+        <v>0.6279225656824035</v>
       </c>
       <c r="U22">
         <v>0.1468</v>
       </c>
       <c r="V22">
-        <v>0.2936131613405207</v>
+        <v>0.2796315822290673</v>
       </c>
       <c r="W22">
-        <v>0.1036975879152116</v>
+        <v>0.1057500837287729</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.9175411291891272</v>
+        <v>0.8738486944658352</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09645024174788011</v>
+        <v>0.09746024174788012</v>
       </c>
       <c r="C23">
-        <v>719.2812294970969</v>
+        <v>688.2531259846022</v>
       </c>
       <c r="D23">
-        <v>957.2542294970968</v>
+        <v>938.5391259846022</v>
       </c>
       <c r="E23">
-        <v>73.07299999999998</v>
+        <v>85.38599999999997</v>
       </c>
       <c r="F23">
-        <v>258.573</v>
+        <v>270.886</v>
       </c>
       <c r="G23">
         <v>20.6</v>
@@ -3304,37 +3304,37 @@
         <v>33.17</v>
       </c>
       <c r="M23">
-        <v>37.9585164</v>
+        <v>39.7660648</v>
       </c>
       <c r="N23">
-        <v>-4.788516399999999</v>
+        <v>-6.596064800000001</v>
       </c>
       <c r="O23">
-        <v>-1.532325248</v>
+        <v>-2.110740736</v>
       </c>
       <c r="P23">
-        <v>-3.256191152</v>
+        <v>-4.485324064</v>
       </c>
       <c r="Q23">
-        <v>2.473808848000001</v>
+        <v>1.244675936</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09397813185422507</v>
+        <v>0.09459580021133052</v>
       </c>
       <c r="T23">
-        <v>0.6279225656824035</v>
+        <v>0.635972854986024</v>
       </c>
       <c r="U23">
         <v>0.1468</v>
       </c>
       <c r="V23">
-        <v>0.2796315822290673</v>
+        <v>0.2669210557641097</v>
       </c>
       <c r="W23">
-        <v>0.1057500837287729</v>
+        <v>0.1076159890138287</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.8738486944658354</v>
+        <v>0.8341282992628428</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09746024174788012</v>
+        <v>0.1115287918765614</v>
       </c>
       <c r="C24">
-        <v>688.2531259846022</v>
+        <v>475.0557895367332</v>
       </c>
       <c r="D24">
-        <v>938.5391259846022</v>
+        <v>737.6547895367332</v>
       </c>
       <c r="E24">
-        <v>85.38599999999997</v>
+        <v>97.69900000000001</v>
       </c>
       <c r="F24">
-        <v>270.886</v>
+        <v>283.199</v>
       </c>
       <c r="G24">
         <v>20.6</v>
@@ -3386,45 +3386,45 @@
         <v>33.17</v>
       </c>
       <c r="M24">
-        <v>39.7660648</v>
+        <v>56.86635920000001</v>
       </c>
       <c r="N24">
-        <v>-6.596064800000001</v>
+        <v>-23.6963592</v>
       </c>
       <c r="O24">
-        <v>-2.110740736</v>
+        <v>-7.582834944000001</v>
       </c>
       <c r="P24">
-        <v>-4.485324064</v>
+        <v>-16.113524256</v>
       </c>
       <c r="Q24">
-        <v>1.244675936</v>
+        <v>-10.383524256</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09459580021133052</v>
+        <v>0.09605879778379108</v>
       </c>
       <c r="T24">
-        <v>0.635972854986024</v>
+        <v>0.655040617764086</v>
       </c>
       <c r="U24">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.2669210557641097</v>
+        <v>0.186655170989037</v>
       </c>
       <c r="W24">
-        <v>0.1076159890138287</v>
+        <v>0.1633196416654014</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y24">
-        <v>0.8341282992628428</v>
+        <v>0.5832974093407408</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1115287918765614</v>
+        <v>0.1130787918765614</v>
       </c>
       <c r="C25">
-        <v>475.0557895367332</v>
+        <v>445.7483564934093</v>
       </c>
       <c r="D25">
-        <v>737.6547895367332</v>
+        <v>720.6603564934093</v>
       </c>
       <c r="E25">
-        <v>97.69900000000001</v>
+        <v>110.012</v>
       </c>
       <c r="F25">
-        <v>283.199</v>
+        <v>295.512</v>
       </c>
       <c r="G25">
         <v>20.6</v>
@@ -3468,37 +3468,37 @@
         <v>33.17</v>
       </c>
       <c r="M25">
-        <v>56.86635920000001</v>
+        <v>59.3388096</v>
       </c>
       <c r="N25">
-        <v>-23.6963592</v>
+        <v>-26.1688096</v>
       </c>
       <c r="O25">
-        <v>-7.582834944000001</v>
+        <v>-8.374019072000001</v>
       </c>
       <c r="P25">
-        <v>-16.113524256</v>
+        <v>-17.794790528</v>
       </c>
       <c r="Q25">
-        <v>-10.383524256</v>
+        <v>-12.064790528</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09605879778379108</v>
+        <v>0.09672009775463042</v>
       </c>
       <c r="T25">
-        <v>0.655040617764086</v>
+        <v>0.6636595732609818</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.186655170989037</v>
+        <v>0.1788778721978272</v>
       </c>
       <c r="W25">
-        <v>0.1633196416654014</v>
+        <v>0.1648813232626763</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5832974093407408</v>
+        <v>0.5589933506182099</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1130787918765614</v>
+        <v>0.1146287918765614</v>
       </c>
       <c r="C26">
-        <v>445.7483564934093</v>
+        <v>417.2063406686354</v>
       </c>
       <c r="D26">
-        <v>720.6603564934093</v>
+        <v>704.4313406686354</v>
       </c>
       <c r="E26">
-        <v>110.012</v>
+        <v>122.325</v>
       </c>
       <c r="F26">
-        <v>295.512</v>
+        <v>307.825</v>
       </c>
       <c r="G26">
         <v>20.6</v>
@@ -3550,37 +3550,37 @@
         <v>33.17</v>
       </c>
       <c r="M26">
-        <v>59.3388096</v>
+        <v>61.81126</v>
       </c>
       <c r="N26">
-        <v>-26.1688096</v>
+        <v>-28.64126</v>
       </c>
       <c r="O26">
-        <v>-8.374019072000001</v>
+        <v>-9.165203199999999</v>
       </c>
       <c r="P26">
-        <v>-17.794790528</v>
+        <v>-19.47605679999999</v>
       </c>
       <c r="Q26">
-        <v>-12.064790528</v>
+        <v>-13.74605679999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09672009775463042</v>
+        <v>0.09739903239135883</v>
       </c>
       <c r="T26">
-        <v>0.6636595732609818</v>
+        <v>0.6725083675711283</v>
       </c>
       <c r="U26">
         <v>0.2008</v>
       </c>
       <c r="V26">
-        <v>0.1788778721978272</v>
+        <v>0.1717227573099141</v>
       </c>
       <c r="W26">
-        <v>0.1648813232626763</v>
+        <v>0.1663180703321693</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.5589933506182099</v>
+        <v>0.5366336165934815</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1146287918765614</v>
+        <v>0.1161787918765615</v>
       </c>
       <c r="C27">
-        <v>417.2063406686354</v>
+        <v>389.3791701504568</v>
       </c>
       <c r="D27">
-        <v>704.4313406686354</v>
+        <v>688.9171701504567</v>
       </c>
       <c r="E27">
-        <v>122.325</v>
+        <v>134.638</v>
       </c>
       <c r="F27">
-        <v>307.825</v>
+        <v>320.138</v>
       </c>
       <c r="G27">
         <v>20.6</v>
@@ -3632,37 +3632,37 @@
         <v>33.17</v>
       </c>
       <c r="M27">
-        <v>61.81126</v>
+        <v>64.2837104</v>
       </c>
       <c r="N27">
-        <v>-28.64126</v>
+        <v>-31.1137104</v>
       </c>
       <c r="O27">
-        <v>-9.165203199999999</v>
+        <v>-9.956387328000002</v>
       </c>
       <c r="P27">
-        <v>-19.47605679999999</v>
+        <v>-21.157323072</v>
       </c>
       <c r="Q27">
-        <v>-13.74605679999999</v>
+        <v>-15.427323072</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09739903239135883</v>
+        <v>0.09809631661286369</v>
       </c>
       <c r="T27">
-        <v>0.6725083675711283</v>
+        <v>0.6815963184842516</v>
       </c>
       <c r="U27">
         <v>0.2008</v>
       </c>
       <c r="V27">
-        <v>0.1717227573099141</v>
+        <v>0.1651180358749174</v>
       </c>
       <c r="W27">
-        <v>0.1663180703321693</v>
+        <v>0.1676442983963166</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.5366336165934815</v>
+        <v>0.5159938621091169</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1161787918765615</v>
+        <v>0.1274364545663146</v>
       </c>
       <c r="C28">
-        <v>389.3791701504568</v>
+        <v>282.0645294749283</v>
       </c>
       <c r="D28">
-        <v>688.9171701504567</v>
+        <v>593.9155294749283</v>
       </c>
       <c r="E28">
-        <v>134.638</v>
+        <v>146.951</v>
       </c>
       <c r="F28">
-        <v>320.138</v>
+        <v>332.451</v>
       </c>
       <c r="G28">
         <v>20.6</v>
@@ -3714,45 +3714,45 @@
         <v>33.17</v>
       </c>
       <c r="M28">
-        <v>64.2837104</v>
+        <v>78.3919458</v>
       </c>
       <c r="N28">
-        <v>-31.1137104</v>
+        <v>-45.2219458</v>
       </c>
       <c r="O28">
-        <v>-9.956387328000002</v>
+        <v>-14.471022656</v>
       </c>
       <c r="P28">
-        <v>-21.157323072</v>
+        <v>-30.750923144</v>
       </c>
       <c r="Q28">
-        <v>-15.427323072</v>
+        <v>-25.020923144</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09809631661286369</v>
+        <v>0.09916566710037296</v>
       </c>
       <c r="T28">
-        <v>0.6815963184842516</v>
+        <v>0.6955335401217001</v>
       </c>
       <c r="U28">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.1651180358749174</v>
+        <v>0.1354016652052538</v>
       </c>
       <c r="W28">
-        <v>0.1676442983963166</v>
+        <v>0.2038722873446012</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.5159938621091169</v>
+        <v>0.4231302037664181</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1274364545663146</v>
+        <v>0.1293364545663146</v>
       </c>
       <c r="C29">
-        <v>282.0645294749283</v>
+        <v>256.2431813907208</v>
       </c>
       <c r="D29">
-        <v>593.9155294749283</v>
+        <v>580.4071813907208</v>
       </c>
       <c r="E29">
-        <v>146.951</v>
+        <v>159.264</v>
       </c>
       <c r="F29">
-        <v>332.451</v>
+        <v>344.764</v>
       </c>
       <c r="G29">
         <v>20.6</v>
@@ -3796,37 +3796,37 @@
         <v>33.17</v>
       </c>
       <c r="M29">
-        <v>78.3919458</v>
+        <v>81.2953512</v>
       </c>
       <c r="N29">
-        <v>-45.2219458</v>
+        <v>-48.1253512</v>
       </c>
       <c r="O29">
-        <v>-14.471022656</v>
+        <v>-15.400112384</v>
       </c>
       <c r="P29">
-        <v>-30.750923144</v>
+        <v>-32.725238816</v>
       </c>
       <c r="Q29">
-        <v>-25.020923144</v>
+        <v>-26.995238816</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09916566710037296</v>
+        <v>0.09990685692121147</v>
       </c>
       <c r="T29">
-        <v>0.6955335401217001</v>
+        <v>0.7051937281789459</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.1354016652052538</v>
+        <v>0.1305658914479233</v>
       </c>
       <c r="W29">
-        <v>0.2038722873446012</v>
+        <v>0.2050125627965797</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.4231302037664181</v>
+        <v>0.4080184107747603</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1293364545663146</v>
+        <v>0.1312364545663146</v>
       </c>
       <c r="C30">
-        <v>256.2431813907208</v>
+        <v>231.022650872979</v>
       </c>
       <c r="D30">
-        <v>580.4071813907208</v>
+        <v>567.499650872979</v>
       </c>
       <c r="E30">
-        <v>159.264</v>
+        <v>171.5770000000001</v>
       </c>
       <c r="F30">
-        <v>344.764</v>
+        <v>357.0770000000001</v>
       </c>
       <c r="G30">
         <v>20.6</v>
@@ -3878,37 +3878,37 @@
         <v>33.17</v>
       </c>
       <c r="M30">
-        <v>81.2953512</v>
+        <v>84.19875660000001</v>
       </c>
       <c r="N30">
-        <v>-48.1253512</v>
+        <v>-51.02875660000001</v>
       </c>
       <c r="O30">
-        <v>-15.400112384</v>
+        <v>-16.329202112</v>
       </c>
       <c r="P30">
-        <v>-32.725238816</v>
+        <v>-34.699554488</v>
       </c>
       <c r="Q30">
-        <v>-26.995238816</v>
+        <v>-28.969554488</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09990685692121147</v>
+        <v>0.1006689253285525</v>
       </c>
       <c r="T30">
-        <v>0.7051937281789459</v>
+        <v>0.7151260342096353</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.1305658914479233</v>
+        <v>0.1260636193290294</v>
       </c>
       <c r="W30">
-        <v>0.2050125627965797</v>
+        <v>0.2060741985622149</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.4080184107747603</v>
+        <v>0.3939488104032168</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1312364545663146</v>
+        <v>0.1331364545663146</v>
       </c>
       <c r="C31">
-        <v>231.0226508729792</v>
+        <v>206.3637256575246</v>
       </c>
       <c r="D31">
-        <v>567.4996508729791</v>
+        <v>555.1537256575245</v>
       </c>
       <c r="E31">
-        <v>171.5769999999999</v>
+        <v>183.89</v>
       </c>
       <c r="F31">
-        <v>357.0769999999999</v>
+        <v>369.39</v>
       </c>
       <c r="G31">
         <v>20.6</v>
@@ -3960,37 +3960,37 @@
         <v>33.17</v>
       </c>
       <c r="M31">
-        <v>84.1987566</v>
+        <v>87.10216200000001</v>
       </c>
       <c r="N31">
-        <v>-51.02875659999999</v>
+        <v>-53.93216200000001</v>
       </c>
       <c r="O31">
-        <v>-16.329202112</v>
+        <v>-17.25829184</v>
       </c>
       <c r="P31">
-        <v>-34.699554488</v>
+        <v>-36.67387016000001</v>
       </c>
       <c r="Q31">
-        <v>-28.969554488</v>
+        <v>-30.94387016000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1006689253285525</v>
+        <v>0.1014527671189604</v>
       </c>
       <c r="T31">
-        <v>0.7151260342096353</v>
+        <v>0.7253421204126301</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.1260636193290294</v>
+        <v>0.1218614986847284</v>
       </c>
       <c r="W31">
-        <v>0.2060741985622149</v>
+        <v>0.207065058610141</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3939488104032168</v>
+        <v>0.3808171833897762</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1331364545663146</v>
+        <v>0.1350364545663146</v>
       </c>
       <c r="C32">
-        <v>206.3637256575246</v>
+        <v>182.2305330705875</v>
       </c>
       <c r="D32">
-        <v>555.1537256575245</v>
+        <v>543.3335330705875</v>
       </c>
       <c r="E32">
-        <v>183.89</v>
+        <v>196.203</v>
       </c>
       <c r="F32">
-        <v>369.39</v>
+        <v>381.703</v>
       </c>
       <c r="G32">
         <v>20.6</v>
@@ -4042,37 +4042,37 @@
         <v>33.17</v>
       </c>
       <c r="M32">
-        <v>87.10216200000001</v>
+        <v>90.0055674</v>
       </c>
       <c r="N32">
-        <v>-53.93216200000001</v>
+        <v>-56.8355674</v>
       </c>
       <c r="O32">
-        <v>-17.25829184</v>
+        <v>-18.187381568</v>
       </c>
       <c r="P32">
-        <v>-36.67387016000001</v>
+        <v>-38.648185832</v>
       </c>
       <c r="Q32">
-        <v>-30.94387016000001</v>
+        <v>-32.91818583199999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1014527671189604</v>
+        <v>0.1022593289612641</v>
       </c>
       <c r="T32">
-        <v>0.7253421204126301</v>
+        <v>0.7358543250562914</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.1218614986847284</v>
+        <v>0.1179304825981243</v>
       </c>
       <c r="W32">
-        <v>0.207065058610141</v>
+        <v>0.2079919922033623</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3808171833897762</v>
+        <v>0.3685327581191383</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1350364545663146</v>
+        <v>0.1369364545663146</v>
       </c>
       <c r="C33">
-        <v>182.2305330705875</v>
+        <v>158.5901919122484</v>
       </c>
       <c r="D33">
-        <v>543.3335330705875</v>
+        <v>532.0061919122484</v>
       </c>
       <c r="E33">
-        <v>196.203</v>
+        <v>208.516</v>
       </c>
       <c r="F33">
-        <v>381.703</v>
+        <v>394.016</v>
       </c>
       <c r="G33">
         <v>20.6</v>
@@ -4124,37 +4124,37 @@
         <v>33.17</v>
       </c>
       <c r="M33">
-        <v>90.0055674</v>
+        <v>92.90897280000002</v>
       </c>
       <c r="N33">
-        <v>-56.8355674</v>
+        <v>-59.73897280000001</v>
       </c>
       <c r="O33">
-        <v>-18.187381568</v>
+        <v>-19.116471296</v>
       </c>
       <c r="P33">
-        <v>-38.648185832</v>
+        <v>-40.62250150400001</v>
       </c>
       <c r="Q33">
-        <v>-32.91818583199999</v>
+        <v>-34.89250150400001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1022593289612641</v>
+        <v>0.1030896132106945</v>
       </c>
       <c r="T33">
-        <v>0.7358543250562914</v>
+        <v>0.7466757121894722</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.1179304825981243</v>
+        <v>0.1142451550169329</v>
       </c>
       <c r="W33">
-        <v>0.2079919922033623</v>
+        <v>0.2088609924470072</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3685327581191383</v>
+        <v>0.3570161094279152</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1369364545663146</v>
+        <v>0.1388364545663146</v>
       </c>
       <c r="C34">
-        <v>158.5901919122484</v>
+        <v>135.4125069955119</v>
       </c>
       <c r="D34">
-        <v>532.0061919122484</v>
+        <v>521.1415069955119</v>
       </c>
       <c r="E34">
-        <v>208.516</v>
+        <v>220.829</v>
       </c>
       <c r="F34">
-        <v>394.016</v>
+        <v>406.329</v>
       </c>
       <c r="G34">
         <v>20.6</v>
@@ -4206,37 +4206,37 @@
         <v>33.17</v>
       </c>
       <c r="M34">
-        <v>92.90897280000002</v>
+        <v>95.81237820000001</v>
       </c>
       <c r="N34">
-        <v>-59.73897280000001</v>
+        <v>-62.64237820000001</v>
       </c>
       <c r="O34">
-        <v>-19.116471296</v>
+        <v>-20.045561024</v>
       </c>
       <c r="P34">
-        <v>-40.62250150400001</v>
+        <v>-42.596817176</v>
       </c>
       <c r="Q34">
-        <v>-34.89250150400001</v>
+        <v>-36.866817176</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1030896132106945</v>
+        <v>0.1039446820645855</v>
       </c>
       <c r="T34">
-        <v>0.7466757121894722</v>
+        <v>0.7578201258042405</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.1142451550169329</v>
+        <v>0.1107831806224804</v>
       </c>
       <c r="W34">
-        <v>0.2088609924470072</v>
+        <v>0.2096773260092191</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3570161094279152</v>
+        <v>0.3461974394452512</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1388364545663146</v>
+        <v>0.1407364545663146</v>
       </c>
       <c r="C35">
-        <v>135.4125069955119</v>
+        <v>112.6697003652272</v>
       </c>
       <c r="D35">
-        <v>521.1415069955119</v>
+        <v>510.7117003652273</v>
       </c>
       <c r="E35">
-        <v>220.829</v>
+        <v>233.142</v>
       </c>
       <c r="F35">
-        <v>406.329</v>
+        <v>418.642</v>
       </c>
       <c r="G35">
         <v>20.6</v>
@@ -4288,37 +4288,37 @@
         <v>33.17</v>
       </c>
       <c r="M35">
-        <v>95.81237820000001</v>
+        <v>98.71578360000001</v>
       </c>
       <c r="N35">
-        <v>-62.64237820000001</v>
+        <v>-65.54578360000001</v>
       </c>
       <c r="O35">
-        <v>-20.045561024</v>
+        <v>-20.974650752</v>
       </c>
       <c r="P35">
-        <v>-42.596817176</v>
+        <v>-44.571132848</v>
       </c>
       <c r="Q35">
-        <v>-36.866817176</v>
+        <v>-38.841132848</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1039446820645855</v>
+        <v>0.1048256620958671</v>
       </c>
       <c r="T35">
-        <v>0.7578201258042405</v>
+        <v>0.7693022489224866</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.1107831806224804</v>
+        <v>0.1075248517806427</v>
       </c>
       <c r="W35">
-        <v>0.2096773260092191</v>
+        <v>0.2104456399501244</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3461974394452512</v>
+        <v>0.3360151618145084</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1407364545663146</v>
+        <v>0.1426364545663146</v>
       </c>
       <c r="C36">
-        <v>112.6697003652272</v>
+        <v>90.33617415906156</v>
       </c>
       <c r="D36">
-        <v>510.7117003652273</v>
+        <v>500.6911741590616</v>
       </c>
       <c r="E36">
-        <v>233.142</v>
+        <v>245.455</v>
       </c>
       <c r="F36">
-        <v>418.642</v>
+        <v>430.955</v>
       </c>
       <c r="G36">
         <v>20.6</v>
@@ -4370,37 +4370,37 @@
         <v>33.17</v>
       </c>
       <c r="M36">
-        <v>98.71578360000001</v>
+        <v>101.619189</v>
       </c>
       <c r="N36">
-        <v>-65.54578360000001</v>
+        <v>-68.44918900000002</v>
       </c>
       <c r="O36">
-        <v>-20.974650752</v>
+        <v>-21.90374048000001</v>
       </c>
       <c r="P36">
-        <v>-44.571132848</v>
+        <v>-46.54544852000001</v>
       </c>
       <c r="Q36">
-        <v>-38.841132848</v>
+        <v>-40.81544852</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1048256620958671</v>
+        <v>0.1057337492050343</v>
       </c>
       <c r="T36">
-        <v>0.7693022489224866</v>
+        <v>0.7811376681366786</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.1075248517806427</v>
+        <v>0.1044527131583386</v>
       </c>
       <c r="W36">
-        <v>0.2104456399501244</v>
+        <v>0.2111700502372638</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3360151618145084</v>
+        <v>0.3264147286198081</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1426364545663146</v>
+        <v>0.1445364545663146</v>
       </c>
       <c r="C37">
-        <v>90.33617415906156</v>
+        <v>68.38830084827947</v>
       </c>
       <c r="D37">
-        <v>500.6911741590616</v>
+        <v>491.0563008482795</v>
       </c>
       <c r="E37">
-        <v>245.455</v>
+        <v>257.768</v>
       </c>
       <c r="F37">
-        <v>430.955</v>
+        <v>443.268</v>
       </c>
       <c r="G37">
         <v>20.6</v>
@@ -4452,37 +4452,37 @@
         <v>33.17</v>
       </c>
       <c r="M37">
-        <v>101.619189</v>
+        <v>104.5225944</v>
       </c>
       <c r="N37">
-        <v>-68.44918900000002</v>
+        <v>-71.35259440000002</v>
       </c>
       <c r="O37">
-        <v>-21.90374048000001</v>
+        <v>-22.832830208</v>
       </c>
       <c r="P37">
-        <v>-46.54544852000001</v>
+        <v>-48.51976419200001</v>
       </c>
       <c r="Q37">
-        <v>-40.81544852</v>
+        <v>-42.78976419200001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1057337492050343</v>
+        <v>0.1066702140363629</v>
       </c>
       <c r="T37">
-        <v>0.7811376681366786</v>
+        <v>0.7933429442013142</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.1044527131583386</v>
+        <v>0.1015512489039403</v>
       </c>
       <c r="W37">
-        <v>0.2111700502372638</v>
+        <v>0.2118542155084509</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3264147286198081</v>
+        <v>0.3173476528248135</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1445364545663146</v>
+        <v>0.1464364545663146</v>
       </c>
       <c r="C38">
-        <v>68.38830084827953</v>
+        <v>46.80423723984421</v>
       </c>
       <c r="D38">
-        <v>491.0563008482795</v>
+        <v>481.7852372398442</v>
       </c>
       <c r="E38">
-        <v>257.768</v>
+        <v>270.081</v>
       </c>
       <c r="F38">
-        <v>443.268</v>
+        <v>455.581</v>
       </c>
       <c r="G38">
         <v>20.6</v>
@@ -4534,37 +4534,37 @@
         <v>33.17</v>
       </c>
       <c r="M38">
-        <v>104.5225944</v>
+        <v>107.4259998</v>
       </c>
       <c r="N38">
-        <v>-71.3525944</v>
+        <v>-74.2559998</v>
       </c>
       <c r="O38">
-        <v>-22.832830208</v>
+        <v>-23.761919936</v>
       </c>
       <c r="P38">
-        <v>-48.519764192</v>
+        <v>-50.494079864</v>
       </c>
       <c r="Q38">
-        <v>-42.78976419199999</v>
+        <v>-44.764079864</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1066702140363629</v>
+        <v>0.107636407909956</v>
       </c>
       <c r="T38">
-        <v>0.7933429442013141</v>
+        <v>0.8059356893473668</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.1015512489039403</v>
+        <v>0.09880662055518519</v>
       </c>
       <c r="W38">
-        <v>0.2118542155084509</v>
+        <v>0.2125013988730873</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3173476528248136</v>
+        <v>0.3087706892349538</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1464364545663146</v>
+        <v>0.1483364545663146</v>
       </c>
       <c r="C39">
-        <v>46.80423723984421</v>
+        <v>25.56375915775686</v>
       </c>
       <c r="D39">
-        <v>481.7852372398442</v>
+        <v>472.8577591577568</v>
       </c>
       <c r="E39">
-        <v>270.081</v>
+        <v>282.394</v>
       </c>
       <c r="F39">
-        <v>455.581</v>
+        <v>467.894</v>
       </c>
       <c r="G39">
         <v>20.6</v>
@@ -4616,37 +4616,37 @@
         <v>33.17</v>
       </c>
       <c r="M39">
-        <v>107.4259998</v>
+        <v>110.3294052</v>
       </c>
       <c r="N39">
-        <v>-74.2559998</v>
+        <v>-77.15940520000001</v>
       </c>
       <c r="O39">
-        <v>-23.761919936</v>
+        <v>-24.691009664</v>
       </c>
       <c r="P39">
-        <v>-50.494079864</v>
+        <v>-52.468395536</v>
       </c>
       <c r="Q39">
-        <v>-44.764079864</v>
+        <v>-46.738395536</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.107636407909956</v>
+        <v>0.1086337693278585</v>
       </c>
       <c r="T39">
-        <v>0.8059356893473668</v>
+        <v>0.8189346520787759</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.09880662055518519</v>
+        <v>0.09620644633004874</v>
       </c>
       <c r="W39">
-        <v>0.2125013988730873</v>
+        <v>0.2131145199553745</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3087706892349538</v>
+        <v>0.3006451447814023</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1483364545663146</v>
+        <v>0.1502364545663146</v>
       </c>
       <c r="C40">
-        <v>25.56375915775686</v>
+        <v>4.648114170136694</v>
       </c>
       <c r="D40">
-        <v>472.8577591577568</v>
+        <v>464.2551141701367</v>
       </c>
       <c r="E40">
-        <v>282.394</v>
+        <v>294.707</v>
       </c>
       <c r="F40">
-        <v>467.894</v>
+        <v>480.207</v>
       </c>
       <c r="G40">
         <v>20.6</v>
@@ -4698,37 +4698,37 @@
         <v>33.17</v>
       </c>
       <c r="M40">
-        <v>110.3294052</v>
+        <v>113.2328106</v>
       </c>
       <c r="N40">
-        <v>-77.15940520000001</v>
+        <v>-80.06281060000001</v>
       </c>
       <c r="O40">
-        <v>-24.691009664</v>
+        <v>-25.620099392</v>
       </c>
       <c r="P40">
-        <v>-52.468395536</v>
+        <v>-54.44271120800001</v>
       </c>
       <c r="Q40">
-        <v>-46.738395536</v>
+        <v>-48.712711208</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1086337693278585</v>
+        <v>0.1096638311201185</v>
       </c>
       <c r="T40">
-        <v>0.8189346520787759</v>
+        <v>0.8323598103095756</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.09620644633004874</v>
+        <v>0.093739614372868</v>
       </c>
       <c r="W40">
-        <v>0.2131145199553745</v>
+        <v>0.2136961989308777</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3006451447814023</v>
+        <v>0.2929362949152124</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1502364545663146</v>
+        <v>0.1521364545663146</v>
       </c>
       <c r="C41">
-        <v>4.648114170136694</v>
+        <v>-15.96010989503253</v>
       </c>
       <c r="D41">
-        <v>464.2551141701367</v>
+        <v>455.9598901049674</v>
       </c>
       <c r="E41">
-        <v>294.707</v>
+        <v>307.02</v>
       </c>
       <c r="F41">
-        <v>480.207</v>
+        <v>492.52</v>
       </c>
       <c r="G41">
         <v>20.6</v>
@@ -4780,37 +4780,37 @@
         <v>33.17</v>
       </c>
       <c r="M41">
-        <v>113.2328106</v>
+        <v>116.136216</v>
       </c>
       <c r="N41">
-        <v>-80.06281060000001</v>
+        <v>-82.966216</v>
       </c>
       <c r="O41">
-        <v>-25.620099392</v>
+        <v>-26.54918912</v>
       </c>
       <c r="P41">
-        <v>-54.44271120800001</v>
+        <v>-56.41702688</v>
       </c>
       <c r="Q41">
-        <v>-48.712711208</v>
+        <v>-50.68702688</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1096638311201185</v>
+        <v>0.1107282283054538</v>
       </c>
       <c r="T41">
-        <v>0.8323598103095756</v>
+        <v>0.8462324738147351</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.093739614372868</v>
+        <v>0.09139612401354631</v>
       </c>
       <c r="W41">
-        <v>0.2136961989308777</v>
+        <v>0.2142487939576058</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2929362949152124</v>
+        <v>0.2856128875423322</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1521364545663146</v>
+        <v>0.1540364545663146</v>
       </c>
       <c r="C42">
-        <v>-15.96010989503253</v>
+        <v>-36.27710258557903</v>
       </c>
       <c r="D42">
-        <v>455.9598901049674</v>
+        <v>447.955897414421</v>
       </c>
       <c r="E42">
-        <v>307.02</v>
+        <v>319.333</v>
       </c>
       <c r="F42">
-        <v>492.52</v>
+        <v>504.833</v>
       </c>
       <c r="G42">
         <v>20.6</v>
@@ -4862,37 +4862,37 @@
         <v>33.17</v>
       </c>
       <c r="M42">
-        <v>116.136216</v>
+        <v>119.0396214</v>
       </c>
       <c r="N42">
-        <v>-82.966216</v>
+        <v>-85.86962140000001</v>
       </c>
       <c r="O42">
-        <v>-26.54918912</v>
+        <v>-27.47827884800001</v>
       </c>
       <c r="P42">
-        <v>-56.41702688</v>
+        <v>-58.39134255200001</v>
       </c>
       <c r="Q42">
-        <v>-50.68702688</v>
+        <v>-52.66134255200001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1107282283054538</v>
+        <v>0.1118287067513089</v>
       </c>
       <c r="T42">
-        <v>0.8462324738147351</v>
+        <v>0.8605753970997307</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.09139612401354631</v>
+        <v>0.08916695025711834</v>
       </c>
       <c r="W42">
-        <v>0.2142487939576058</v>
+        <v>0.2147744331293715</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2856128875423322</v>
+        <v>0.2786467195534948</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1540364545663146</v>
+        <v>0.1559364545663146</v>
       </c>
       <c r="C43">
-        <v>-36.27710258557903</v>
+        <v>-56.31793628459224</v>
       </c>
       <c r="D43">
-        <v>447.955897414421</v>
+        <v>440.2280637154078</v>
       </c>
       <c r="E43">
-        <v>319.333</v>
+        <v>331.6460000000001</v>
       </c>
       <c r="F43">
-        <v>504.833</v>
+        <v>517.1460000000001</v>
       </c>
       <c r="G43">
         <v>20.6</v>
@@ -4944,37 +4944,37 @@
         <v>33.17</v>
       </c>
       <c r="M43">
-        <v>119.0396214</v>
+        <v>121.9430268</v>
       </c>
       <c r="N43">
-        <v>-85.86962140000001</v>
+        <v>-88.77302680000003</v>
       </c>
       <c r="O43">
-        <v>-27.47827884800001</v>
+        <v>-28.40736857600001</v>
       </c>
       <c r="P43">
-        <v>-58.39134255200001</v>
+        <v>-60.36565822400001</v>
       </c>
       <c r="Q43">
-        <v>-52.66134255200001</v>
+        <v>-54.63565822400001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1118287067513089</v>
+        <v>0.1129671327297798</v>
       </c>
       <c r="T43">
-        <v>0.8605753970997307</v>
+        <v>0.8754129039462778</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.08916695025711834</v>
+        <v>0.08704392763194883</v>
       </c>
       <c r="W43">
-        <v>0.2147744331293715</v>
+        <v>0.2152750418643865</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2786467195534948</v>
+        <v>0.2720122738498402</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1559364545663146</v>
+        <v>0.1578364545663146</v>
       </c>
       <c r="C44">
-        <v>-56.31793628459212</v>
+        <v>-76.09666093909885</v>
       </c>
       <c r="D44">
-        <v>440.2280637154078</v>
+        <v>432.7623390609011</v>
       </c>
       <c r="E44">
-        <v>331.646</v>
+        <v>343.9589999999999</v>
       </c>
       <c r="F44">
-        <v>517.146</v>
+        <v>529.4589999999999</v>
       </c>
       <c r="G44">
         <v>20.6</v>
@@ -5026,37 +5026,37 @@
         <v>33.17</v>
       </c>
       <c r="M44">
-        <v>121.9430268</v>
+        <v>124.8464322</v>
       </c>
       <c r="N44">
-        <v>-88.7730268</v>
+        <v>-91.67643219999999</v>
       </c>
       <c r="O44">
-        <v>-28.407368576</v>
+        <v>-29.336458304</v>
       </c>
       <c r="P44">
-        <v>-60.365658224</v>
+        <v>-62.339973896</v>
       </c>
       <c r="Q44">
-        <v>-54.635658224</v>
+        <v>-56.609973896</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1129671327297798</v>
+        <v>0.114145503479425</v>
       </c>
       <c r="T44">
-        <v>0.8754129039462777</v>
+        <v>0.8907710250681421</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.08704392763194886</v>
+        <v>0.08501965024515937</v>
       </c>
       <c r="W44">
-        <v>0.2152750418643865</v>
+        <v>0.2157523664721914</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2720122738498402</v>
+        <v>0.265686407016123</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1578364545663146</v>
+        <v>0.1597364545663146</v>
       </c>
       <c r="C45">
-        <v>-76.09666093909885</v>
+        <v>-95.62638931058899</v>
       </c>
       <c r="D45">
-        <v>432.7623390609011</v>
+        <v>425.5456106894109</v>
       </c>
       <c r="E45">
-        <v>343.9589999999999</v>
+        <v>356.2719999999999</v>
       </c>
       <c r="F45">
-        <v>529.4589999999999</v>
+        <v>541.7719999999999</v>
       </c>
       <c r="G45">
         <v>20.6</v>
@@ -5108,37 +5108,37 @@
         <v>33.17</v>
       </c>
       <c r="M45">
-        <v>124.8464322</v>
+        <v>127.7498376</v>
       </c>
       <c r="N45">
-        <v>-91.67643219999999</v>
+        <v>-94.57983759999999</v>
       </c>
       <c r="O45">
-        <v>-29.336458304</v>
+        <v>-30.265548032</v>
       </c>
       <c r="P45">
-        <v>-62.339973896</v>
+        <v>-64.31428956799999</v>
       </c>
       <c r="Q45">
-        <v>-56.609973896</v>
+        <v>-58.58428956799999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.114145503479425</v>
+        <v>0.1153659588987005</v>
       </c>
       <c r="T45">
-        <v>0.8907710250681421</v>
+        <v>0.9066776505157875</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.08501965024515937</v>
+        <v>0.08308738546686029</v>
       </c>
       <c r="W45">
-        <v>0.2157523664721914</v>
+        <v>0.2162079945069143</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.265686407016123</v>
+        <v>0.2596480795839384</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1597364545663146</v>
+        <v>0.1616364545663146</v>
       </c>
       <c r="C46">
-        <v>-95.62638931058899</v>
+        <v>-114.9193738356421</v>
       </c>
       <c r="D46">
-        <v>425.5456106894109</v>
+        <v>418.5656261643579</v>
       </c>
       <c r="E46">
-        <v>356.2719999999999</v>
+        <v>368.585</v>
       </c>
       <c r="F46">
-        <v>541.7719999999999</v>
+        <v>554.085</v>
       </c>
       <c r="G46">
         <v>20.6</v>
@@ -5190,37 +5190,37 @@
         <v>33.17</v>
       </c>
       <c r="M46">
-        <v>127.7498376</v>
+        <v>130.653243</v>
       </c>
       <c r="N46">
-        <v>-94.57983759999999</v>
+        <v>-97.483243</v>
       </c>
       <c r="O46">
-        <v>-30.265548032</v>
+        <v>-31.19463776</v>
       </c>
       <c r="P46">
-        <v>-64.31428956799999</v>
+        <v>-66.28860524</v>
       </c>
       <c r="Q46">
-        <v>-58.58428956799999</v>
+        <v>-60.55860523999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1153659588987005</v>
+        <v>0.1166307945150405</v>
       </c>
       <c r="T46">
-        <v>0.9066776505157875</v>
+        <v>0.9231626987069836</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.08308738546686029</v>
+        <v>0.08124099912315227</v>
       </c>
       <c r="W46">
-        <v>0.2162079945069143</v>
+        <v>0.2166433724067607</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2596480795839384</v>
+        <v>0.2538781222598508</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1616364545663146</v>
+        <v>0.1635364545663146</v>
       </c>
       <c r="C47">
-        <v>-114.9193738356421</v>
+        <v>-133.987076044416</v>
       </c>
       <c r="D47">
-        <v>418.5656261643579</v>
+        <v>411.810923955584</v>
       </c>
       <c r="E47">
-        <v>368.585</v>
+        <v>380.898</v>
       </c>
       <c r="F47">
-        <v>554.085</v>
+        <v>566.398</v>
       </c>
       <c r="G47">
         <v>20.6</v>
@@ -5272,37 +5272,37 @@
         <v>33.17</v>
       </c>
       <c r="M47">
-        <v>130.653243</v>
+        <v>133.5566484</v>
       </c>
       <c r="N47">
-        <v>-97.483243</v>
+        <v>-100.3866484</v>
       </c>
       <c r="O47">
-        <v>-31.19463776</v>
+        <v>-32.123727488</v>
       </c>
       <c r="P47">
-        <v>-66.28860524</v>
+        <v>-68.262920912</v>
       </c>
       <c r="Q47">
-        <v>-60.55860523999999</v>
+        <v>-62.53292091199999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1166307945150405</v>
+        <v>0.1179424758949486</v>
       </c>
       <c r="T47">
-        <v>0.9231626987069836</v>
+        <v>0.9402583042385946</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.08124099912315227</v>
+        <v>0.079474890446562</v>
       </c>
       <c r="W47">
-        <v>0.2166433724067607</v>
+        <v>0.2170598208327007</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2538781222598508</v>
+        <v>0.2483590326455063</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1635364545663146</v>
+        <v>0.1654364545663146</v>
       </c>
       <c r="C48">
-        <v>-133.987076044416</v>
+        <v>-152.8402293643381</v>
       </c>
       <c r="D48">
-        <v>411.810923955584</v>
+        <v>405.2707706356619</v>
       </c>
       <c r="E48">
-        <v>380.898</v>
+        <v>393.211</v>
       </c>
       <c r="F48">
-        <v>566.398</v>
+        <v>578.711</v>
       </c>
       <c r="G48">
         <v>20.6</v>
@@ -5354,37 +5354,37 @@
         <v>33.17</v>
       </c>
       <c r="M48">
-        <v>133.5566484</v>
+        <v>136.4600538</v>
       </c>
       <c r="N48">
-        <v>-100.3866484</v>
+        <v>-103.2900538</v>
       </c>
       <c r="O48">
-        <v>-32.123727488</v>
+        <v>-33.052817216</v>
       </c>
       <c r="P48">
-        <v>-68.262920912</v>
+        <v>-70.23723658399999</v>
       </c>
       <c r="Q48">
-        <v>-62.53292091199999</v>
+        <v>-64.50723658399998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1179424758949486</v>
+        <v>0.1193036546854193</v>
       </c>
       <c r="T48">
-        <v>0.9402583042385946</v>
+        <v>0.9579990269600774</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.079474890446562</v>
+        <v>0.07778393533067771</v>
       </c>
       <c r="W48">
-        <v>0.2170598208327007</v>
+        <v>0.2174585480490262</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2483590326455063</v>
+        <v>0.2430747979083678</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1654364545663146</v>
+        <v>0.1673364545663146</v>
       </c>
       <c r="C49">
-        <v>-152.8402293643381</v>
+        <v>-171.4888960328736</v>
       </c>
       <c r="D49">
-        <v>405.2707706356619</v>
+        <v>398.9351039671264</v>
       </c>
       <c r="E49">
-        <v>393.211</v>
+        <v>405.524</v>
       </c>
       <c r="F49">
-        <v>578.711</v>
+        <v>591.024</v>
       </c>
       <c r="G49">
         <v>20.6</v>
@@ -5436,37 +5436,37 @@
         <v>33.17</v>
       </c>
       <c r="M49">
-        <v>136.4600538</v>
+        <v>139.3634592</v>
       </c>
       <c r="N49">
-        <v>-103.2900538</v>
+        <v>-106.1934592</v>
       </c>
       <c r="O49">
-        <v>-33.052817216</v>
+        <v>-33.981906944</v>
       </c>
       <c r="P49">
-        <v>-70.23723658399999</v>
+        <v>-72.211552256</v>
       </c>
       <c r="Q49">
-        <v>-64.50723658399998</v>
+        <v>-66.481552256</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1193036546854193</v>
+        <v>0.1207171865062928</v>
       </c>
       <c r="T49">
-        <v>0.9579990269600774</v>
+        <v>0.9764220851708482</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.07778393533067771</v>
+        <v>0.07616343667795526</v>
       </c>
       <c r="W49">
-        <v>0.2174585480490262</v>
+        <v>0.2178406616313382</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2430747979083678</v>
+        <v>0.2380107396186102</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1673364545663146</v>
+        <v>0.1692364545663146</v>
       </c>
       <c r="C50">
-        <v>-171.4888960328734</v>
+        <v>-189.9425187540999</v>
       </c>
       <c r="D50">
-        <v>398.9351039671266</v>
+        <v>392.7944812459001</v>
       </c>
       <c r="E50">
-        <v>405.524</v>
+        <v>417.837</v>
       </c>
       <c r="F50">
-        <v>591.024</v>
+        <v>603.337</v>
       </c>
       <c r="G50">
         <v>20.6</v>
@@ -5518,37 +5518,37 @@
         <v>33.17</v>
       </c>
       <c r="M50">
-        <v>139.3634592</v>
+        <v>142.2668646</v>
       </c>
       <c r="N50">
-        <v>-106.1934592</v>
+        <v>-109.0968646</v>
       </c>
       <c r="O50">
-        <v>-33.981906944</v>
+        <v>-34.910996672</v>
       </c>
       <c r="P50">
-        <v>-72.211552256</v>
+        <v>-74.18586792799999</v>
       </c>
       <c r="Q50">
-        <v>-66.481552256</v>
+        <v>-68.45586792799999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1207171865062928</v>
+        <v>0.1221861509475927</v>
       </c>
       <c r="T50">
-        <v>0.9764220851708482</v>
+        <v>0.9955676162526296</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07616343667795526</v>
+        <v>0.07460908082738475</v>
       </c>
       <c r="W50">
-        <v>0.2178406616313382</v>
+        <v>0.2182071787409027</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2380107396186102</v>
+        <v>0.2331533775855773</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1692364545663146</v>
+        <v>0.1711364545663146</v>
       </c>
       <c r="C51">
-        <v>-189.9425187540999</v>
+        <v>-208.2099676568517</v>
       </c>
       <c r="D51">
-        <v>392.7944812459001</v>
+        <v>386.8400323431482</v>
       </c>
       <c r="E51">
-        <v>417.837</v>
+        <v>430.15</v>
       </c>
       <c r="F51">
-        <v>603.337</v>
+        <v>615.65</v>
       </c>
       <c r="G51">
         <v>20.6</v>
@@ -5600,37 +5600,37 @@
         <v>33.17</v>
       </c>
       <c r="M51">
-        <v>142.2668646</v>
+        <v>145.17027</v>
       </c>
       <c r="N51">
-        <v>-109.0968646</v>
+        <v>-112.00027</v>
       </c>
       <c r="O51">
-        <v>-34.910996672</v>
+        <v>-35.8400864</v>
       </c>
       <c r="P51">
-        <v>-74.18586792799999</v>
+        <v>-76.16018359999998</v>
       </c>
       <c r="Q51">
-        <v>-68.45586792799999</v>
+        <v>-70.43018359999998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1221861509475927</v>
+        <v>0.1237138739665445</v>
       </c>
       <c r="T51">
-        <v>0.9955676162526296</v>
+        <v>1.015478968577682</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07460908082738475</v>
+        <v>0.07311689921083706</v>
       </c>
       <c r="W51">
-        <v>0.2182071787409027</v>
+        <v>0.2185590351660846</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2331533775855773</v>
+        <v>0.2284903100338658</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1711364545663146</v>
+        <v>0.1730364545663146</v>
       </c>
       <c r="C52">
-        <v>-208.2099676568517</v>
+        <v>-226.2995830455562</v>
       </c>
       <c r="D52">
-        <v>386.8400323431482</v>
+        <v>381.0634169544438</v>
       </c>
       <c r="E52">
-        <v>430.15</v>
+        <v>442.463</v>
       </c>
       <c r="F52">
-        <v>615.65</v>
+        <v>627.963</v>
       </c>
       <c r="G52">
         <v>20.6</v>
@@ -5682,37 +5682,37 @@
         <v>33.17</v>
       </c>
       <c r="M52">
-        <v>145.17027</v>
+        <v>148.0736754</v>
       </c>
       <c r="N52">
-        <v>-112.00027</v>
+        <v>-114.9036754</v>
       </c>
       <c r="O52">
-        <v>-35.8400864</v>
+        <v>-36.769176128</v>
       </c>
       <c r="P52">
-        <v>-76.16018359999998</v>
+        <v>-78.13449927199999</v>
       </c>
       <c r="Q52">
-        <v>-70.43018359999998</v>
+        <v>-72.40449927199998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1237138739665445</v>
+        <v>0.1253039530270862</v>
       </c>
       <c r="T52">
-        <v>1.015478968577682</v>
+        <v>1.0362030291609</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.07311689921083706</v>
+        <v>0.07168323452042849</v>
       </c>
       <c r="W52">
-        <v>0.2185590351660846</v>
+        <v>0.218897093300083</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2284903100338658</v>
+        <v>0.224010107876339</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1730364545663146</v>
+        <v>0.1749364545663146</v>
       </c>
       <c r="C53">
-        <v>-226.2995830455562</v>
+        <v>-244.2192143770803</v>
       </c>
       <c r="D53">
-        <v>381.0634169544438</v>
+        <v>375.4567856229196</v>
       </c>
       <c r="E53">
-        <v>442.463</v>
+        <v>454.776</v>
       </c>
       <c r="F53">
-        <v>627.963</v>
+        <v>640.276</v>
       </c>
       <c r="G53">
         <v>20.6</v>
@@ -5764,37 +5764,37 @@
         <v>33.17</v>
       </c>
       <c r="M53">
-        <v>148.0736754</v>
+        <v>150.9770808</v>
       </c>
       <c r="N53">
-        <v>-114.9036754</v>
+        <v>-117.8070808</v>
       </c>
       <c r="O53">
-        <v>-36.769176128</v>
+        <v>-37.69826585599999</v>
       </c>
       <c r="P53">
-        <v>-78.13449927199999</v>
+        <v>-80.10881494399999</v>
       </c>
       <c r="Q53">
-        <v>-72.40449927199998</v>
+        <v>-74.37881494399998</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1253039530270862</v>
+        <v>0.1269602853818172</v>
       </c>
       <c r="T53">
-        <v>1.0362030291609</v>
+        <v>1.057790592268419</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.07168323452042849</v>
+        <v>0.07030471077965102</v>
       </c>
       <c r="W53">
-        <v>0.218897093300083</v>
+        <v>0.2192221491981583</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.224010107876339</v>
+        <v>0.2197022211864094</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1749364545663146</v>
+        <v>0.1768364545663146</v>
       </c>
       <c r="C54">
-        <v>-244.2192143770803</v>
+        <v>-261.9762558466437</v>
       </c>
       <c r="D54">
-        <v>375.4567856229196</v>
+        <v>370.0127441533563</v>
       </c>
       <c r="E54">
-        <v>454.776</v>
+        <v>467.0890000000001</v>
       </c>
       <c r="F54">
-        <v>640.276</v>
+        <v>652.5890000000001</v>
       </c>
       <c r="G54">
         <v>20.6</v>
@@ -5846,37 +5846,37 @@
         <v>33.17</v>
       </c>
       <c r="M54">
-        <v>150.9770808</v>
+        <v>153.8804862</v>
       </c>
       <c r="N54">
-        <v>-117.8070808</v>
+        <v>-120.7104862</v>
       </c>
       <c r="O54">
-        <v>-37.69826585599999</v>
+        <v>-38.627355584</v>
       </c>
       <c r="P54">
-        <v>-80.10881494399999</v>
+        <v>-82.08313061600001</v>
       </c>
       <c r="Q54">
-        <v>-74.37881494399998</v>
+        <v>-76.353130616</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1269602853818172</v>
+        <v>0.1286870999644091</v>
       </c>
       <c r="T54">
-        <v>1.057790592268419</v>
+        <v>1.080296775082641</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.07030471077965102</v>
+        <v>0.06897820680267645</v>
       </c>
       <c r="W54">
-        <v>0.2192221491981583</v>
+        <v>0.2195349388359289</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2197022211864094</v>
+        <v>0.2155568962583639</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1768364545663146</v>
+        <v>0.1787364545663146</v>
       </c>
       <c r="C55">
-        <v>-261.9762558466437</v>
+        <v>-279.5776789220513</v>
       </c>
       <c r="D55">
-        <v>370.0127441533563</v>
+        <v>364.7243210779487</v>
       </c>
       <c r="E55">
-        <v>467.0890000000001</v>
+        <v>479.402</v>
       </c>
       <c r="F55">
-        <v>652.5890000000001</v>
+        <v>664.902</v>
       </c>
       <c r="G55">
         <v>20.6</v>
@@ -5928,37 +5928,37 @@
         <v>33.17</v>
       </c>
       <c r="M55">
-        <v>153.8804862</v>
+        <v>156.7838916</v>
       </c>
       <c r="N55">
-        <v>-120.7104862</v>
+        <v>-123.6138916</v>
       </c>
       <c r="O55">
-        <v>-38.627355584</v>
+        <v>-39.556445312</v>
       </c>
       <c r="P55">
-        <v>-82.08313061600001</v>
+        <v>-84.05744628799999</v>
       </c>
       <c r="Q55">
-        <v>-76.353130616</v>
+        <v>-78.32744628799999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1286870999644091</v>
+        <v>0.1304889934418962</v>
       </c>
       <c r="T55">
-        <v>1.080296775082641</v>
+        <v>1.103781487584437</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06897820680267645</v>
+        <v>0.0677008326026269</v>
       </c>
       <c r="W55">
-        <v>0.2195349388359289</v>
+        <v>0.2198361436723006</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2155568962583639</v>
+        <v>0.211565101883209</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1787364545663146</v>
+        <v>0.1806364545663146</v>
       </c>
       <c r="C56">
-        <v>-279.5776789220513</v>
+        <v>-297.0300621272608</v>
       </c>
       <c r="D56">
-        <v>364.7243210779487</v>
+        <v>359.5849378727392</v>
       </c>
       <c r="E56">
-        <v>479.402</v>
+        <v>491.715</v>
       </c>
       <c r="F56">
-        <v>664.902</v>
+        <v>677.215</v>
       </c>
       <c r="G56">
         <v>20.6</v>
@@ -6010,37 +6010,37 @@
         <v>33.17</v>
       </c>
       <c r="M56">
-        <v>156.7838916</v>
+        <v>159.687297</v>
       </c>
       <c r="N56">
-        <v>-123.6138916</v>
+        <v>-126.517297</v>
       </c>
       <c r="O56">
-        <v>-39.556445312</v>
+        <v>-40.48553504</v>
       </c>
       <c r="P56">
-        <v>-84.05744628799999</v>
+        <v>-86.03176196</v>
       </c>
       <c r="Q56">
-        <v>-78.32744628799999</v>
+        <v>-80.30176195999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1304889934418962</v>
+        <v>0.1323709710739384</v>
       </c>
       <c r="T56">
-        <v>1.103781487584437</v>
+        <v>1.128309965086314</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.0677008326026269</v>
+        <v>0.06646990837348822</v>
       </c>
       <c r="W56">
-        <v>0.2198361436723006</v>
+        <v>0.2201263956055315</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.211565101883209</v>
+        <v>0.2077184636671507</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1806364545663146</v>
+        <v>0.1825364545663146</v>
       </c>
       <c r="C57">
-        <v>-297.0300621272608</v>
+        <v>-314.3396183428299</v>
       </c>
       <c r="D57">
-        <v>359.5849378727392</v>
+        <v>354.5883816571701</v>
       </c>
       <c r="E57">
-        <v>491.715</v>
+        <v>504.028</v>
       </c>
       <c r="F57">
-        <v>677.215</v>
+        <v>689.528</v>
       </c>
       <c r="G57">
         <v>20.6</v>
@@ -6092,37 +6092,37 @@
         <v>33.17</v>
       </c>
       <c r="M57">
-        <v>159.687297</v>
+        <v>162.5907024</v>
       </c>
       <c r="N57">
-        <v>-126.517297</v>
+        <v>-129.4207024</v>
       </c>
       <c r="O57">
-        <v>-40.48553504</v>
+        <v>-41.414624768</v>
       </c>
       <c r="P57">
-        <v>-86.03176196</v>
+        <v>-88.00607763199999</v>
       </c>
       <c r="Q57">
-        <v>-80.30176195999999</v>
+        <v>-82.27607763199998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1323709710739384</v>
+        <v>0.1343384931438006</v>
       </c>
       <c r="T57">
-        <v>1.128309965086314</v>
+        <v>1.15395337338373</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06646990837348822</v>
+        <v>0.06528294572396165</v>
       </c>
       <c r="W57">
-        <v>0.2201263956055315</v>
+        <v>0.2204062813982899</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2077184636671507</v>
+        <v>0.2040092053873802</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1825364545663146</v>
+        <v>0.1844364545663146</v>
       </c>
       <c r="C58">
-        <v>-314.3396183428299</v>
+        <v>-331.5122198614648</v>
       </c>
       <c r="D58">
-        <v>354.5883816571701</v>
+        <v>349.7287801385352</v>
       </c>
       <c r="E58">
-        <v>504.028</v>
+        <v>516.341</v>
       </c>
       <c r="F58">
-        <v>689.528</v>
+        <v>701.841</v>
       </c>
       <c r="G58">
         <v>20.6</v>
@@ -6174,37 +6174,37 @@
         <v>33.17</v>
       </c>
       <c r="M58">
-        <v>162.5907024</v>
+        <v>165.4941078</v>
       </c>
       <c r="N58">
-        <v>-129.4207024</v>
+        <v>-132.3241078</v>
       </c>
       <c r="O58">
-        <v>-41.414624768</v>
+        <v>-42.343714496</v>
       </c>
       <c r="P58">
-        <v>-88.00607763199999</v>
+        <v>-89.98039330399999</v>
       </c>
       <c r="Q58">
-        <v>-82.27607763199998</v>
+        <v>-84.25039330399999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1343384931438006</v>
+        <v>0.136397527868075</v>
       </c>
       <c r="T58">
-        <v>1.15395337338373</v>
+        <v>1.180789498346142</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06528294572396165</v>
+        <v>0.06413763088669916</v>
       </c>
       <c r="W58">
-        <v>0.2204062813982899</v>
+        <v>0.2206763466369163</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2040092053873802</v>
+        <v>0.200430096520935</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1844364545663146</v>
+        <v>0.1863364545663146</v>
       </c>
       <c r="C59">
-        <v>-331.5122198614648</v>
+        <v>-348.5534214111181</v>
       </c>
       <c r="D59">
-        <v>349.7287801385352</v>
+        <v>345.000578588882</v>
       </c>
       <c r="E59">
-        <v>516.341</v>
+        <v>528.6540000000001</v>
       </c>
       <c r="F59">
-        <v>701.841</v>
+        <v>714.1540000000001</v>
       </c>
       <c r="G59">
         <v>20.6</v>
@@ -6256,37 +6256,37 @@
         <v>33.17</v>
       </c>
       <c r="M59">
-        <v>165.4941078</v>
+        <v>168.3975132</v>
       </c>
       <c r="N59">
-        <v>-132.3241078</v>
+        <v>-135.2275132</v>
       </c>
       <c r="O59">
-        <v>-42.343714496</v>
+        <v>-43.27280422400001</v>
       </c>
       <c r="P59">
-        <v>-89.98039330399999</v>
+        <v>-91.95470897600002</v>
       </c>
       <c r="Q59">
-        <v>-84.25039330399999</v>
+        <v>-86.22470897600002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.136397527868075</v>
+        <v>0.138554611864934</v>
       </c>
       <c r="T59">
-        <v>1.180789498346142</v>
+        <v>1.20890353402105</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06413763088669916</v>
+        <v>0.06303180966451469</v>
       </c>
       <c r="W59">
-        <v>0.2206763466369163</v>
+        <v>0.2209370992811074</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.200430096520935</v>
+        <v>0.1969744052016084</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1863364545663146</v>
+        <v>0.1882364545663146</v>
       </c>
       <c r="C60">
-        <v>-348.5534214111178</v>
+        <v>-365.4684813354171</v>
       </c>
       <c r="D60">
-        <v>345.000578588882</v>
+        <v>340.3985186645829</v>
       </c>
       <c r="E60">
-        <v>528.6539999999999</v>
+        <v>540.967</v>
       </c>
       <c r="F60">
-        <v>714.1539999999999</v>
+        <v>726.467</v>
       </c>
       <c r="G60">
         <v>20.6</v>
@@ -6338,37 +6338,37 @@
         <v>33.17</v>
       </c>
       <c r="M60">
-        <v>168.3975132</v>
+        <v>171.3009186</v>
       </c>
       <c r="N60">
-        <v>-135.2275132</v>
+        <v>-138.1309186</v>
       </c>
       <c r="O60">
-        <v>-43.27280422399999</v>
+        <v>-44.20189395200001</v>
       </c>
       <c r="P60">
-        <v>-91.95470897599998</v>
+        <v>-93.92902464800002</v>
       </c>
       <c r="Q60">
-        <v>-86.22470897599997</v>
+        <v>-88.19902464800002</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.138554611864934</v>
+        <v>0.1408169194713958</v>
       </c>
       <c r="T60">
-        <v>1.20890353402105</v>
+        <v>1.238388986070344</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.06303180966451469</v>
+        <v>0.06196347390748901</v>
       </c>
       <c r="W60">
-        <v>0.2209370992811074</v>
+        <v>0.2211890128526141</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1969744052016085</v>
+        <v>0.193635855960903</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1882364545663146</v>
+        <v>0.1901364545663146</v>
       </c>
       <c r="C61">
-        <v>-365.4684813354171</v>
+        <v>-382.2623811012177</v>
       </c>
       <c r="D61">
-        <v>340.3985186645829</v>
+        <v>335.9176188987823</v>
       </c>
       <c r="E61">
-        <v>540.967</v>
+        <v>553.28</v>
       </c>
       <c r="F61">
-        <v>726.467</v>
+        <v>738.78</v>
       </c>
       <c r="G61">
         <v>20.6</v>
@@ -6420,37 +6420,37 @@
         <v>33.17</v>
       </c>
       <c r="M61">
-        <v>171.3009186</v>
+        <v>174.204324</v>
       </c>
       <c r="N61">
-        <v>-138.1309186</v>
+        <v>-141.034324</v>
       </c>
       <c r="O61">
-        <v>-44.20189395200001</v>
+        <v>-45.13098368000001</v>
       </c>
       <c r="P61">
-        <v>-93.92902464800002</v>
+        <v>-95.90334032000001</v>
       </c>
       <c r="Q61">
-        <v>-88.19902464800002</v>
+        <v>-90.17334032000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1408169194713958</v>
+        <v>0.1431923424581806</v>
       </c>
       <c r="T61">
-        <v>1.238388986070344</v>
+        <v>1.269348710722102</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.06196347390748901</v>
+        <v>0.0609307493423642</v>
       </c>
       <c r="W61">
-        <v>0.2211890128526141</v>
+        <v>0.2214325293050705</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.193635855960903</v>
+        <v>0.190408591694888</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1901364545663146</v>
+        <v>0.1920364545663146</v>
       </c>
       <c r="C62">
-        <v>-382.2623811012177</v>
+        <v>-398.9398432854282</v>
       </c>
       <c r="D62">
-        <v>335.9176188987823</v>
+        <v>331.5531567145717</v>
       </c>
       <c r="E62">
-        <v>553.28</v>
+        <v>565.593</v>
       </c>
       <c r="F62">
-        <v>738.78</v>
+        <v>751.093</v>
       </c>
       <c r="G62">
         <v>20.6</v>
@@ -6502,37 +6502,37 @@
         <v>33.17</v>
       </c>
       <c r="M62">
-        <v>174.204324</v>
+        <v>177.1077294</v>
       </c>
       <c r="N62">
-        <v>-141.034324</v>
+        <v>-143.9377294</v>
       </c>
       <c r="O62">
-        <v>-45.13098368000001</v>
+        <v>-46.06007340800001</v>
       </c>
       <c r="P62">
-        <v>-95.90334032000001</v>
+        <v>-97.87765599200002</v>
       </c>
       <c r="Q62">
-        <v>-90.17334032000001</v>
+        <v>-92.14765599200001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1431923424581806</v>
+        <v>0.1456895820083904</v>
       </c>
       <c r="T62">
-        <v>1.269348710722102</v>
+        <v>1.301896113561131</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.0609307493423642</v>
+        <v>0.05993188459904675</v>
       </c>
       <c r="W62">
-        <v>0.2214325293050705</v>
+        <v>0.2216680616115448</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.190408591694888</v>
+        <v>0.187287139372021</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1920364545663146</v>
+        <v>0.1939364545663146</v>
       </c>
       <c r="C63">
-        <v>-398.9398432854282</v>
+        <v>-415.5053481776368</v>
       </c>
       <c r="D63">
-        <v>331.5531567145717</v>
+        <v>327.3006518223631</v>
       </c>
       <c r="E63">
-        <v>565.593</v>
+        <v>577.9059999999999</v>
       </c>
       <c r="F63">
-        <v>751.093</v>
+        <v>763.4059999999999</v>
       </c>
       <c r="G63">
         <v>20.6</v>
@@ -6584,37 +6584,37 @@
         <v>33.17</v>
       </c>
       <c r="M63">
-        <v>177.1077294</v>
+        <v>180.0111348</v>
       </c>
       <c r="N63">
-        <v>-143.9377294</v>
+        <v>-146.8411348</v>
       </c>
       <c r="O63">
-        <v>-46.06007340800001</v>
+        <v>-46.98916313600001</v>
       </c>
       <c r="P63">
-        <v>-97.87765599200002</v>
+        <v>-99.85197166400002</v>
       </c>
       <c r="Q63">
-        <v>-92.14765599200001</v>
+        <v>-94.12197166400001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1456895820083904</v>
+        <v>0.1483182552191375</v>
       </c>
       <c r="T63">
-        <v>1.301896113561131</v>
+        <v>1.336156537602213</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05993188459904675</v>
+        <v>0.05896524129906213</v>
       </c>
       <c r="W63">
-        <v>0.2216680616115448</v>
+        <v>0.2218959961016812</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.187287139372021</v>
+        <v>0.1842663790595691</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1939364545663146</v>
+        <v>0.1958364545663146</v>
       </c>
       <c r="C64">
-        <v>-415.5053481776368</v>
+        <v>-431.9631491212475</v>
       </c>
       <c r="D64">
-        <v>327.3006518223631</v>
+        <v>323.1558508787524</v>
       </c>
       <c r="E64">
-        <v>577.9059999999999</v>
+        <v>590.2189999999999</v>
       </c>
       <c r="F64">
-        <v>763.4059999999999</v>
+        <v>775.7189999999999</v>
       </c>
       <c r="G64">
         <v>20.6</v>
@@ -6666,37 +6666,37 @@
         <v>33.17</v>
       </c>
       <c r="M64">
-        <v>180.0111348</v>
+        <v>182.9145402</v>
       </c>
       <c r="N64">
-        <v>-146.8411348</v>
+        <v>-149.7445402</v>
       </c>
       <c r="O64">
-        <v>-46.98916313600001</v>
+        <v>-47.91825286400001</v>
       </c>
       <c r="P64">
-        <v>-99.85197166400002</v>
+        <v>-101.826287336</v>
       </c>
       <c r="Q64">
-        <v>-94.12197166400001</v>
+        <v>-96.096287336</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1483182552191375</v>
+        <v>0.1510890188737088</v>
       </c>
       <c r="T64">
-        <v>1.336156537602213</v>
+        <v>1.372268876456327</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05896524129906213</v>
+        <v>0.05802928508796591</v>
       </c>
       <c r="W64">
-        <v>0.2218959961016812</v>
+        <v>0.2221166945762577</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1842663790595691</v>
+        <v>0.1813415158998933</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1958364545663146</v>
+        <v>0.1977364545663146</v>
       </c>
       <c r="C65">
-        <v>-431.9631491212475</v>
+        <v>-448.3172867035495</v>
       </c>
       <c r="D65">
-        <v>323.1558508787524</v>
+        <v>319.1147132964505</v>
       </c>
       <c r="E65">
-        <v>590.2189999999999</v>
+        <v>602.532</v>
       </c>
       <c r="F65">
-        <v>775.7189999999999</v>
+        <v>788.032</v>
       </c>
       <c r="G65">
         <v>20.6</v>
@@ -6748,37 +6748,37 @@
         <v>33.17</v>
       </c>
       <c r="M65">
-        <v>182.9145402</v>
+        <v>185.8179456</v>
       </c>
       <c r="N65">
-        <v>-149.7445402</v>
+        <v>-152.6479456</v>
       </c>
       <c r="O65">
-        <v>-47.91825286400001</v>
+        <v>-48.847342592</v>
       </c>
       <c r="P65">
-        <v>-101.826287336</v>
+        <v>-103.800603008</v>
       </c>
       <c r="Q65">
-        <v>-96.096287336</v>
+        <v>-98.07060300800001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1510890188737088</v>
+        <v>0.154013713842423</v>
       </c>
       <c r="T65">
-        <v>1.372268876456327</v>
+        <v>1.410387456357892</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05802928508796591</v>
+        <v>0.05712257750846643</v>
       </c>
       <c r="W65">
-        <v>0.2221166945762577</v>
+        <v>0.2223304962235036</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1813415158998933</v>
+        <v>0.1785080547139577</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1977364545663146</v>
+        <v>0.1996364545663146</v>
       </c>
       <c r="C66">
-        <v>-448.3172867035495</v>
+        <v>-464.5716018942339</v>
       </c>
       <c r="D66">
-        <v>319.1147132964505</v>
+        <v>315.1733981057661</v>
       </c>
       <c r="E66">
-        <v>602.532</v>
+        <v>614.845</v>
       </c>
       <c r="F66">
-        <v>788.032</v>
+        <v>800.345</v>
       </c>
       <c r="G66">
         <v>20.6</v>
@@ -6830,37 +6830,37 @@
         <v>33.17</v>
       </c>
       <c r="M66">
-        <v>185.8179456</v>
+        <v>188.721351</v>
       </c>
       <c r="N66">
-        <v>-152.6479456</v>
+        <v>-155.551351</v>
       </c>
       <c r="O66">
-        <v>-48.847342592</v>
+        <v>-49.77643232</v>
       </c>
       <c r="P66">
-        <v>-103.800603008</v>
+        <v>-105.77491868</v>
       </c>
       <c r="Q66">
-        <v>-98.07060300800001</v>
+        <v>-100.04491868</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.154013713842423</v>
+        <v>0.1571055342379208</v>
       </c>
       <c r="T66">
-        <v>1.410387456357892</v>
+        <v>1.45068424082526</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05712257750846643</v>
+        <v>0.0562437686237208</v>
       </c>
       <c r="W66">
-        <v>0.2223304962235036</v>
+        <v>0.2225377193585266</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1785080547139577</v>
+        <v>0.1757617769491275</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1996364545663146</v>
+        <v>0.2015364545663146</v>
       </c>
       <c r="C67">
-        <v>-464.5716018942339</v>
+        <v>-480.7297482221668</v>
       </c>
       <c r="D67">
-        <v>315.1733981057661</v>
+        <v>311.3282517778331</v>
       </c>
       <c r="E67">
-        <v>614.845</v>
+        <v>627.158</v>
       </c>
       <c r="F67">
-        <v>800.345</v>
+        <v>812.658</v>
       </c>
       <c r="G67">
         <v>20.6</v>
@@ -6912,37 +6912,37 @@
         <v>33.17</v>
       </c>
       <c r="M67">
-        <v>188.721351</v>
+        <v>191.6247564</v>
       </c>
       <c r="N67">
-        <v>-155.551351</v>
+        <v>-158.4547564</v>
       </c>
       <c r="O67">
-        <v>-49.77643232</v>
+        <v>-50.70552204800001</v>
       </c>
       <c r="P67">
-        <v>-105.77491868</v>
+        <v>-107.749234352</v>
       </c>
       <c r="Q67">
-        <v>-100.04491868</v>
+        <v>-102.019234352</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1571055342379208</v>
+        <v>0.160379226421389</v>
       </c>
       <c r="T67">
-        <v>1.45068424082526</v>
+        <v>1.493351424378945</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.0562437686237208</v>
+        <v>0.05539159031124018</v>
       </c>
       <c r="W67">
-        <v>0.2225377193585266</v>
+        <v>0.2227386630046096</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1757617769491275</v>
+        <v>0.1730987197226256</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2015364545663146</v>
+        <v>0.2034364545663146</v>
       </c>
       <c r="C68">
-        <v>-480.7297482221668</v>
+        <v>-496.795203071556</v>
       </c>
       <c r="D68">
-        <v>311.3282517778331</v>
+        <v>307.5757969284439</v>
       </c>
       <c r="E68">
-        <v>627.158</v>
+        <v>639.471</v>
       </c>
       <c r="F68">
-        <v>812.658</v>
+        <v>824.971</v>
       </c>
       <c r="G68">
         <v>20.6</v>
@@ -6994,37 +6994,37 @@
         <v>33.17</v>
       </c>
       <c r="M68">
-        <v>191.6247564</v>
+        <v>194.5281618</v>
       </c>
       <c r="N68">
-        <v>-158.4547564</v>
+        <v>-161.3581618</v>
       </c>
       <c r="O68">
-        <v>-50.70552204800001</v>
+        <v>-51.634611776</v>
       </c>
       <c r="P68">
-        <v>-107.749234352</v>
+        <v>-109.723550024</v>
       </c>
       <c r="Q68">
-        <v>-102.019234352</v>
+        <v>-103.993550024</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.160379226421389</v>
+        <v>0.1638513241917341</v>
       </c>
       <c r="T68">
-        <v>1.493351424378945</v>
+        <v>1.538604497844973</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.05539159031124018</v>
+        <v>0.05456485015734108</v>
       </c>
       <c r="W68">
-        <v>0.2227386630046096</v>
+        <v>0.222933608332899</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1730987197226256</v>
+        <v>0.1705151567416909</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2034364545663146</v>
+        <v>0.2053364545663146</v>
       </c>
       <c r="C69">
-        <v>-496.795203071556</v>
+        <v>-512.7712781709286</v>
       </c>
       <c r="D69">
-        <v>307.5757969284439</v>
+        <v>303.9127218290714</v>
       </c>
       <c r="E69">
-        <v>639.471</v>
+        <v>651.784</v>
       </c>
       <c r="F69">
-        <v>824.971</v>
+        <v>837.284</v>
       </c>
       <c r="G69">
         <v>20.6</v>
@@ -7076,37 +7076,37 @@
         <v>33.17</v>
       </c>
       <c r="M69">
-        <v>194.5281618</v>
+        <v>197.4315672</v>
       </c>
       <c r="N69">
-        <v>-161.3581618</v>
+        <v>-164.2615672</v>
       </c>
       <c r="O69">
-        <v>-51.634611776</v>
+        <v>-52.563701504</v>
       </c>
       <c r="P69">
-        <v>-109.723550024</v>
+        <v>-111.697865696</v>
       </c>
       <c r="Q69">
-        <v>-103.993550024</v>
+        <v>-105.967865696</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1638513241917341</v>
+        <v>0.1675404280727258</v>
       </c>
       <c r="T69">
-        <v>1.538604497844973</v>
+        <v>1.586685888402628</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05456485015734108</v>
+        <v>0.05376242589032135</v>
       </c>
       <c r="W69">
-        <v>0.222933608332899</v>
+        <v>0.2231228199750623</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1705151567416909</v>
+        <v>0.1680075809072543</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2053364545663146</v>
+        <v>0.2072364545663146</v>
       </c>
       <c r="C70">
-        <v>-512.7712781709286</v>
+        <v>-528.6611293414185</v>
       </c>
       <c r="D70">
-        <v>303.9127218290714</v>
+        <v>300.3358706585817</v>
       </c>
       <c r="E70">
-        <v>651.784</v>
+        <v>664.0970000000001</v>
       </c>
       <c r="F70">
-        <v>837.284</v>
+        <v>849.5970000000001</v>
       </c>
       <c r="G70">
         <v>20.6</v>
@@ -7158,37 +7158,37 @@
         <v>33.17</v>
       </c>
       <c r="M70">
-        <v>197.4315672</v>
+        <v>200.3349726</v>
       </c>
       <c r="N70">
-        <v>-164.2615672</v>
+        <v>-167.1649726000001</v>
       </c>
       <c r="O70">
-        <v>-52.563701504</v>
+        <v>-53.49279123200002</v>
       </c>
       <c r="P70">
-        <v>-111.697865696</v>
+        <v>-113.672181368</v>
       </c>
       <c r="Q70">
-        <v>-105.967865696</v>
+        <v>-107.942181368</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1675404280727258</v>
+        <v>0.171467538655717</v>
       </c>
       <c r="T70">
-        <v>1.586685888402628</v>
+        <v>1.637869304157552</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05376242589032135</v>
+        <v>0.05298326029770799</v>
       </c>
       <c r="W70">
-        <v>0.2231228199750623</v>
+        <v>0.2233065472218005</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1680075809072543</v>
+        <v>0.1655726884303375</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2072364545663146</v>
+        <v>0.2091364545663146</v>
       </c>
       <c r="C71">
-        <v>-528.6611293414185</v>
+        <v>-544.4677655646757</v>
       </c>
       <c r="D71">
-        <v>300.3358706585817</v>
+        <v>296.8422344353244</v>
       </c>
       <c r="E71">
-        <v>664.0970000000001</v>
+        <v>676.4100000000001</v>
       </c>
       <c r="F71">
-        <v>849.5970000000001</v>
+        <v>861.9100000000001</v>
       </c>
       <c r="G71">
         <v>20.6</v>
@@ -7240,37 +7240,37 @@
         <v>33.17</v>
       </c>
       <c r="M71">
-        <v>200.3349726</v>
+        <v>203.238378</v>
       </c>
       <c r="N71">
-        <v>-167.1649726000001</v>
+        <v>-170.0683780000001</v>
       </c>
       <c r="O71">
-        <v>-53.49279123200002</v>
+        <v>-54.42188096000002</v>
       </c>
       <c r="P71">
-        <v>-113.672181368</v>
+        <v>-115.64649704</v>
       </c>
       <c r="Q71">
-        <v>-107.942181368</v>
+        <v>-109.91649704</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.171467538655717</v>
+        <v>0.1756564566109076</v>
       </c>
       <c r="T71">
-        <v>1.637869304157552</v>
+        <v>1.692464947629471</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.05298326029770799</v>
+        <v>0.05222635657916931</v>
       </c>
       <c r="W71">
-        <v>0.2233065472218005</v>
+        <v>0.2234850251186319</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1655726884303375</v>
+        <v>0.163207364309904</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2091364545663146</v>
+        <v>0.2110364545663146</v>
       </c>
       <c r="C72">
-        <v>-544.4677655646757</v>
+        <v>-560.1940574251638</v>
       </c>
       <c r="D72">
-        <v>296.8422344353244</v>
+        <v>293.4289425748362</v>
       </c>
       <c r="E72">
-        <v>676.4100000000001</v>
+        <v>688.7230000000001</v>
       </c>
       <c r="F72">
-        <v>861.9100000000001</v>
+        <v>874.2230000000001</v>
       </c>
       <c r="G72">
         <v>20.6</v>
@@ -7322,37 +7322,37 @@
         <v>33.17</v>
       </c>
       <c r="M72">
-        <v>203.238378</v>
+        <v>206.1417834</v>
       </c>
       <c r="N72">
-        <v>-170.0683780000001</v>
+        <v>-172.9717834</v>
       </c>
       <c r="O72">
-        <v>-54.42188096000002</v>
+        <v>-55.35097068800002</v>
       </c>
       <c r="P72">
-        <v>-115.64649704</v>
+        <v>-117.620812712</v>
       </c>
       <c r="Q72">
-        <v>-109.91649704</v>
+        <v>-111.890812712</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1756564566109076</v>
+        <v>0.1801342654595595</v>
       </c>
       <c r="T72">
-        <v>1.692464947629471</v>
+        <v>1.750825807892556</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.05222635657916931</v>
+        <v>0.05149077409213876</v>
       </c>
       <c r="W72">
-        <v>0.2234850251186319</v>
+        <v>0.2236584754690737</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.163207364309904</v>
+        <v>0.1609086690379335</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2110364545663146</v>
+        <v>0.2129364545663146</v>
       </c>
       <c r="C73">
-        <v>-560.1940574251637</v>
+        <v>-575.8427449766248</v>
       </c>
       <c r="D73">
-        <v>293.4289425748362</v>
+        <v>290.0932550233751</v>
       </c>
       <c r="E73">
-        <v>688.723</v>
+        <v>701.0359999999999</v>
       </c>
       <c r="F73">
-        <v>874.223</v>
+        <v>886.5359999999999</v>
       </c>
       <c r="G73">
         <v>20.6</v>
@@ -7404,37 +7404,37 @@
         <v>33.17</v>
       </c>
       <c r="M73">
-        <v>206.1417834</v>
+        <v>209.0451888</v>
       </c>
       <c r="N73">
-        <v>-172.9717834</v>
+        <v>-175.8751888</v>
       </c>
       <c r="O73">
-        <v>-55.350970688</v>
+        <v>-56.280060416</v>
       </c>
       <c r="P73">
-        <v>-117.620812712</v>
+        <v>-119.595128384</v>
       </c>
       <c r="Q73">
-        <v>-111.890812712</v>
+        <v>-113.865128384</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1801342654595595</v>
+        <v>0.1849319177974009</v>
       </c>
       <c r="T73">
-        <v>1.750825807892555</v>
+        <v>1.813355301031575</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.05149077409213876</v>
+        <v>0.05077562445197017</v>
       </c>
       <c r="W73">
-        <v>0.2236584754690737</v>
+        <v>0.2238271077542255</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1609086690379337</v>
+        <v>0.1586738264124068</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2129364545663146</v>
+        <v>0.2148364545663146</v>
       </c>
       <c r="C74">
-        <v>-575.8427449766248</v>
+        <v>-591.4164450780231</v>
       </c>
       <c r="D74">
-        <v>290.0932550233751</v>
+        <v>286.8325549219768</v>
       </c>
       <c r="E74">
-        <v>701.0359999999999</v>
+        <v>713.3489999999999</v>
       </c>
       <c r="F74">
-        <v>886.5359999999999</v>
+        <v>898.8489999999999</v>
       </c>
       <c r="G74">
         <v>20.6</v>
@@ -7486,37 +7486,37 @@
         <v>33.17</v>
       </c>
       <c r="M74">
-        <v>209.0451888</v>
+        <v>211.9485942</v>
       </c>
       <c r="N74">
-        <v>-175.8751888</v>
+        <v>-178.7785942</v>
       </c>
       <c r="O74">
-        <v>-56.280060416</v>
+        <v>-57.209150144</v>
       </c>
       <c r="P74">
-        <v>-119.595128384</v>
+        <v>-121.569444056</v>
       </c>
       <c r="Q74">
-        <v>-113.865128384</v>
+        <v>-115.839444056</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1849319177974009</v>
+        <v>0.1900849517898973</v>
       </c>
       <c r="T74">
-        <v>1.813355301031575</v>
+        <v>1.880516608477189</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.05077562445197017</v>
+        <v>0.05008006795262811</v>
       </c>
       <c r="W74">
-        <v>0.2238271077542255</v>
+        <v>0.2239911199767703</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1586738264124068</v>
+        <v>0.1565002123519629</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2148364545663146</v>
+        <v>0.2167364545663146</v>
       </c>
       <c r="C75">
-        <v>-591.4164450780231</v>
+        <v>-606.9176582402444</v>
       </c>
       <c r="D75">
-        <v>286.8325549219768</v>
+        <v>283.6443417597555</v>
       </c>
       <c r="E75">
-        <v>713.3489999999999</v>
+        <v>725.6619999999999</v>
       </c>
       <c r="F75">
-        <v>898.8489999999999</v>
+        <v>911.1619999999999</v>
       </c>
       <c r="G75">
         <v>20.6</v>
@@ -7568,37 +7568,37 @@
         <v>33.17</v>
       </c>
       <c r="M75">
-        <v>211.9485942</v>
+        <v>214.8519996</v>
       </c>
       <c r="N75">
-        <v>-178.7785942</v>
+        <v>-181.6819996</v>
       </c>
       <c r="O75">
-        <v>-57.209150144</v>
+        <v>-58.13823987199999</v>
       </c>
       <c r="P75">
-        <v>-121.569444056</v>
+        <v>-123.543759728</v>
       </c>
       <c r="Q75">
-        <v>-115.839444056</v>
+        <v>-117.813759728</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1900849517898973</v>
+        <v>0.1956343730125856</v>
       </c>
       <c r="T75">
-        <v>1.880516608477189</v>
+        <v>1.952844170341696</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.05008006795262811</v>
+        <v>0.04940331027759259</v>
       </c>
       <c r="W75">
-        <v>0.2239911199767703</v>
+        <v>0.2241506994365437</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1565002123519629</v>
+        <v>0.1543853446174769</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2167364545663146</v>
+        <v>0.2186364545663146</v>
       </c>
       <c r="C76">
-        <v>-606.9176582402444</v>
+        <v>-622.3487750211968</v>
       </c>
       <c r="D76">
-        <v>283.6443417597555</v>
+        <v>280.5262249788031</v>
       </c>
       <c r="E76">
-        <v>725.6619999999999</v>
+        <v>737.9749999999999</v>
       </c>
       <c r="F76">
-        <v>911.1619999999999</v>
+        <v>923.4749999999999</v>
       </c>
       <c r="G76">
         <v>20.6</v>
@@ -7650,37 +7650,37 @@
         <v>33.17</v>
       </c>
       <c r="M76">
-        <v>214.8519996</v>
+        <v>217.755405</v>
       </c>
       <c r="N76">
-        <v>-181.6819996</v>
+        <v>-184.585405</v>
       </c>
       <c r="O76">
-        <v>-58.13823987199999</v>
+        <v>-59.06732959999999</v>
       </c>
       <c r="P76">
-        <v>-123.543759728</v>
+        <v>-125.5180754</v>
       </c>
       <c r="Q76">
-        <v>-117.813759728</v>
+        <v>-119.7880754</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1956343730125856</v>
+        <v>0.201627747933089</v>
       </c>
       <c r="T76">
-        <v>1.952844170341696</v>
+        <v>2.030957937155364</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04940331027759259</v>
+        <v>0.04874459947389136</v>
       </c>
       <c r="W76">
-        <v>0.2241506994365437</v>
+        <v>0.2243060234440564</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1543853446174769</v>
+        <v>0.1523268733559106</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2186364545663146</v>
+        <v>0.2205364545663146</v>
       </c>
       <c r="C77">
-        <v>-622.3487750211968</v>
+        <v>-637.7120820036899</v>
       </c>
       <c r="D77">
-        <v>280.5262249788031</v>
+        <v>277.47591799631</v>
       </c>
       <c r="E77">
-        <v>737.9749999999999</v>
+        <v>750.288</v>
       </c>
       <c r="F77">
-        <v>923.4749999999999</v>
+        <v>935.788</v>
       </c>
       <c r="G77">
         <v>20.6</v>
@@ -7732,37 +7732,37 @@
         <v>33.17</v>
       </c>
       <c r="M77">
-        <v>217.755405</v>
+        <v>220.6588104</v>
       </c>
       <c r="N77">
-        <v>-184.585405</v>
+        <v>-187.4888104</v>
       </c>
       <c r="O77">
-        <v>-59.06732959999999</v>
+        <v>-59.99641932800001</v>
       </c>
       <c r="P77">
-        <v>-125.5180754</v>
+        <v>-127.492391072</v>
       </c>
       <c r="Q77">
-        <v>-119.7880754</v>
+        <v>-121.762391072</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.201627747933089</v>
+        <v>0.2081205707636344</v>
       </c>
       <c r="T77">
-        <v>2.030957937155364</v>
+        <v>2.115581184536838</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04874459947389136</v>
+        <v>0.04810322316502437</v>
       </c>
       <c r="W77">
-        <v>0.2243060234440564</v>
+        <v>0.2244572599776873</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1523268733559106</v>
+        <v>0.1503225723907011</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2205364545663146</v>
+        <v>0.2224364545663146</v>
       </c>
       <c r="C78">
-        <v>-637.7120820036899</v>
+        <v>-653.009767387505</v>
       </c>
       <c r="D78">
-        <v>277.47591799631</v>
+        <v>274.491232612495</v>
       </c>
       <c r="E78">
-        <v>750.288</v>
+        <v>762.601</v>
       </c>
       <c r="F78">
-        <v>935.788</v>
+        <v>948.101</v>
       </c>
       <c r="G78">
         <v>20.6</v>
@@ -7814,37 +7814,37 @@
         <v>33.17</v>
       </c>
       <c r="M78">
-        <v>220.6588104</v>
+        <v>223.5622158</v>
       </c>
       <c r="N78">
-        <v>-187.4888104</v>
+        <v>-190.3922158</v>
       </c>
       <c r="O78">
-        <v>-59.99641932800001</v>
+        <v>-60.92550905600001</v>
       </c>
       <c r="P78">
-        <v>-127.492391072</v>
+        <v>-129.466706744</v>
       </c>
       <c r="Q78">
-        <v>-121.762391072</v>
+        <v>-123.736706744</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2081205707636344</v>
+        <v>0.2151779868837924</v>
       </c>
       <c r="T78">
-        <v>2.115581184536838</v>
+        <v>2.207562975168874</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04810322316502437</v>
+        <v>0.04747850598106301</v>
       </c>
       <c r="W78">
-        <v>0.2244572599776873</v>
+        <v>0.2246045682896654</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1503225723907011</v>
+        <v>0.1483703311908219</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2224364545663146</v>
+        <v>0.2243364545663146</v>
       </c>
       <c r="C79">
-        <v>-653.009767387505</v>
+        <v>-668.2439262243969</v>
       </c>
       <c r="D79">
-        <v>274.491232612495</v>
+        <v>271.5700737756031</v>
       </c>
       <c r="E79">
-        <v>762.601</v>
+        <v>774.914</v>
       </c>
       <c r="F79">
-        <v>948.101</v>
+        <v>960.414</v>
       </c>
       <c r="G79">
         <v>20.6</v>
@@ -7896,37 +7896,37 @@
         <v>33.17</v>
       </c>
       <c r="M79">
-        <v>223.5622158</v>
+        <v>226.4656212</v>
       </c>
       <c r="N79">
-        <v>-190.3922158</v>
+        <v>-193.2956212</v>
       </c>
       <c r="O79">
-        <v>-60.92550905600001</v>
+        <v>-61.85459878400001</v>
       </c>
       <c r="P79">
-        <v>-129.466706744</v>
+        <v>-131.441022416</v>
       </c>
       <c r="Q79">
-        <v>-123.736706744</v>
+        <v>-125.711022416</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2151779868837924</v>
+        <v>0.2228769862876012</v>
       </c>
       <c r="T79">
-        <v>2.207562975168874</v>
+        <v>2.30790674676746</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04747850598106301</v>
+        <v>0.046869807186434</v>
       </c>
       <c r="W79">
-        <v>0.2246045682896654</v>
+        <v>0.2247480994654389</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1483703311908219</v>
+        <v>0.1464681474576062</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2243364545663146</v>
+        <v>0.2262364545663146</v>
       </c>
       <c r="C80">
-        <v>-668.2439262243969</v>
+        <v>-683.4165653223488</v>
       </c>
       <c r="D80">
-        <v>271.5700737756031</v>
+        <v>268.7104346776512</v>
       </c>
       <c r="E80">
-        <v>774.914</v>
+        <v>787.227</v>
       </c>
       <c r="F80">
-        <v>960.414</v>
+        <v>972.727</v>
       </c>
       <c r="G80">
         <v>20.6</v>
@@ -7978,37 +7978,37 @@
         <v>33.17</v>
       </c>
       <c r="M80">
-        <v>226.4656212</v>
+        <v>229.3690266</v>
       </c>
       <c r="N80">
-        <v>-193.2956212</v>
+        <v>-196.1990266</v>
       </c>
       <c r="O80">
-        <v>-61.85459878400001</v>
+        <v>-62.78368851200001</v>
       </c>
       <c r="P80">
-        <v>-131.441022416</v>
+        <v>-133.415338088</v>
       </c>
       <c r="Q80">
-        <v>-125.711022416</v>
+        <v>-127.685338088</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2228769862876012</v>
+        <v>0.231309223729868</v>
       </c>
       <c r="T80">
-        <v>2.30790674676746</v>
+        <v>2.417807068042101</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.046869807186434</v>
+        <v>0.04627651848787154</v>
       </c>
       <c r="W80">
-        <v>0.2247480994654389</v>
+        <v>0.2248879969405599</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1464681474576062</v>
+        <v>0.1446141202745985</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2262364545663146</v>
+        <v>0.2281364545663146</v>
       </c>
       <c r="C81">
-        <v>-683.4165653223488</v>
+        <v>-698.5296078432033</v>
       </c>
       <c r="D81">
-        <v>268.7104346776512</v>
+        <v>265.9103921567967</v>
       </c>
       <c r="E81">
-        <v>787.227</v>
+        <v>799.54</v>
       </c>
       <c r="F81">
-        <v>972.727</v>
+        <v>985.04</v>
       </c>
       <c r="G81">
         <v>20.6</v>
@@ -8060,37 +8060,37 @@
         <v>33.17</v>
       </c>
       <c r="M81">
-        <v>229.3690266</v>
+        <v>232.272432</v>
       </c>
       <c r="N81">
-        <v>-196.1990266</v>
+        <v>-199.102432</v>
       </c>
       <c r="O81">
-        <v>-62.78368851200001</v>
+        <v>-63.71277824000001</v>
       </c>
       <c r="P81">
-        <v>-133.415338088</v>
+        <v>-135.38965376</v>
       </c>
       <c r="Q81">
-        <v>-127.685338088</v>
+        <v>-129.65965376</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.231309223729868</v>
+        <v>0.2405846849163614</v>
       </c>
       <c r="T81">
-        <v>2.417807068042101</v>
+        <v>2.538697421444206</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04627651848787154</v>
+        <v>0.04569806200677316</v>
       </c>
       <c r="W81">
-        <v>0.2248879969405599</v>
+        <v>0.2250243969788029</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1446141202745985</v>
+        <v>0.142806443771166</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2281364545663146</v>
+        <v>0.2300364545663146</v>
       </c>
       <c r="C82">
-        <v>-698.5296078432033</v>
+        <v>-713.5848976158068</v>
       </c>
       <c r="D82">
-        <v>265.9103921567967</v>
+        <v>263.1681023841933</v>
       </c>
       <c r="E82">
-        <v>799.54</v>
+        <v>811.8530000000001</v>
       </c>
       <c r="F82">
-        <v>985.04</v>
+        <v>997.3530000000001</v>
       </c>
       <c r="G82">
         <v>20.6</v>
@@ -8142,37 +8142,37 @@
         <v>33.17</v>
       </c>
       <c r="M82">
-        <v>232.272432</v>
+        <v>235.1758374</v>
       </c>
       <c r="N82">
-        <v>-199.102432</v>
+        <v>-202.0058374</v>
       </c>
       <c r="O82">
-        <v>-63.71277824000001</v>
+        <v>-64.64186796800001</v>
       </c>
       <c r="P82">
-        <v>-135.38965376</v>
+        <v>-137.363969432</v>
       </c>
       <c r="Q82">
-        <v>-129.65965376</v>
+        <v>-131.633969432</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2405846849163614</v>
+        <v>0.2508365104382751</v>
       </c>
       <c r="T82">
-        <v>2.538697421444206</v>
+        <v>2.672313075204427</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04569806200677316</v>
+        <v>0.04513388840175126</v>
       </c>
       <c r="W82">
-        <v>0.2250243969788029</v>
+        <v>0.2251574291148671</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.142806443771166</v>
+        <v>0.1410434012554728</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2300364545663146</v>
+        <v>0.2319364545663146</v>
       </c>
       <c r="C83">
-        <v>-713.5848976158068</v>
+        <v>-728.5842031849924</v>
       </c>
       <c r="D83">
-        <v>263.1681023841933</v>
+        <v>260.4817968150077</v>
       </c>
       <c r="E83">
-        <v>811.8530000000001</v>
+        <v>824.1660000000001</v>
       </c>
       <c r="F83">
-        <v>997.3530000000001</v>
+        <v>1009.666</v>
       </c>
       <c r="G83">
         <v>20.6</v>
@@ -8224,37 +8224,37 @@
         <v>33.17</v>
       </c>
       <c r="M83">
-        <v>235.1758374</v>
+        <v>238.0792428</v>
       </c>
       <c r="N83">
-        <v>-202.0058374</v>
+        <v>-204.9092428</v>
       </c>
       <c r="O83">
-        <v>-64.64186796800001</v>
+        <v>-65.57095769600001</v>
       </c>
       <c r="P83">
-        <v>-137.363969432</v>
+        <v>-139.338285104</v>
       </c>
       <c r="Q83">
-        <v>-131.633969432</v>
+        <v>-133.608285104</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2508365104382751</v>
+        <v>0.2622274276848459</v>
       </c>
       <c r="T83">
-        <v>2.672313075204427</v>
+        <v>2.820774912715784</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04513388840175126</v>
+        <v>0.04458347512855917</v>
       </c>
       <c r="W83">
-        <v>0.2251574291148671</v>
+        <v>0.2252872165646858</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1410434012554728</v>
+        <v>0.1393233597767475</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2319364545663146</v>
+        <v>0.2338364545663146</v>
       </c>
       <c r="C84">
-        <v>-728.5842031849924</v>
+        <v>-743.5292216150888</v>
       </c>
       <c r="D84">
-        <v>260.4817968150077</v>
+        <v>257.8497783849113</v>
       </c>
       <c r="E84">
-        <v>824.1660000000001</v>
+        <v>836.479</v>
       </c>
       <c r="F84">
-        <v>1009.666</v>
+        <v>1021.979</v>
       </c>
       <c r="G84">
         <v>20.6</v>
@@ -8306,37 +8306,37 @@
         <v>33.17</v>
       </c>
       <c r="M84">
-        <v>238.0792428</v>
+        <v>240.9826482</v>
       </c>
       <c r="N84">
-        <v>-204.9092428</v>
+        <v>-207.8126482</v>
       </c>
       <c r="O84">
-        <v>-65.57095769600001</v>
+        <v>-66.500047424</v>
       </c>
       <c r="P84">
-        <v>-139.338285104</v>
+        <v>-141.312600776</v>
       </c>
       <c r="Q84">
-        <v>-133.608285104</v>
+        <v>-135.582600776</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2622274276848459</v>
+        <v>0.2749584528427781</v>
       </c>
       <c r="T84">
-        <v>2.820774912715784</v>
+        <v>2.98670284875789</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04458347512855917</v>
+        <v>0.04404632482580544</v>
       </c>
       <c r="W84">
-        <v>0.2252872165646858</v>
+        <v>0.2254138766060751</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1393233597767475</v>
+        <v>0.1376447650806421</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2338364545663146</v>
+        <v>0.2357364545663146</v>
       </c>
       <c r="C85">
-        <v>-743.5292216150888</v>
+        <v>-758.4215820651402</v>
       </c>
       <c r="D85">
-        <v>257.8497783849113</v>
+        <v>255.2704179348599</v>
       </c>
       <c r="E85">
-        <v>836.479</v>
+        <v>848.7920000000001</v>
       </c>
       <c r="F85">
-        <v>1021.979</v>
+        <v>1034.292</v>
       </c>
       <c r="G85">
         <v>20.6</v>
@@ -8388,37 +8388,37 @@
         <v>33.17</v>
       </c>
       <c r="M85">
-        <v>240.9826482</v>
+        <v>243.8860536000001</v>
       </c>
       <c r="N85">
-        <v>-207.8126482</v>
+        <v>-210.7160536000001</v>
       </c>
       <c r="O85">
-        <v>-66.500047424</v>
+        <v>-67.42913715200002</v>
       </c>
       <c r="P85">
-        <v>-141.312600776</v>
+        <v>-143.2869164480001</v>
       </c>
       <c r="Q85">
-        <v>-135.582600776</v>
+        <v>-137.5569164480001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2749584528427781</v>
+        <v>0.2892808561454517</v>
       </c>
       <c r="T85">
-        <v>2.98670284875789</v>
+        <v>3.173371776805258</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04404632482580544</v>
+        <v>0.04352196381597442</v>
       </c>
       <c r="W85">
-        <v>0.2254138766060751</v>
+        <v>0.2255375209321933</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1376447650806421</v>
+        <v>0.13600613692492</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2357364545663146</v>
+        <v>0.2376364545663146</v>
       </c>
       <c r="C86">
-        <v>-758.42158206514</v>
+        <v>-773.2628491516681</v>
       </c>
       <c r="D86">
-        <v>255.2704179348599</v>
+        <v>252.7421508483319</v>
       </c>
       <c r="E86">
-        <v>848.7919999999999</v>
+        <v>861.105</v>
       </c>
       <c r="F86">
-        <v>1034.292</v>
+        <v>1046.605</v>
       </c>
       <c r="G86">
         <v>20.6</v>
@@ -8470,37 +8470,37 @@
         <v>33.17</v>
       </c>
       <c r="M86">
-        <v>243.8860536</v>
+        <v>246.789459</v>
       </c>
       <c r="N86">
-        <v>-210.7160536</v>
+        <v>-213.619459</v>
       </c>
       <c r="O86">
-        <v>-67.42913715200001</v>
+        <v>-68.35822688</v>
       </c>
       <c r="P86">
-        <v>-143.286916448</v>
+        <v>-145.26123212</v>
       </c>
       <c r="Q86">
-        <v>-137.556916448</v>
+        <v>-139.53123212</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2892808561454516</v>
+        <v>0.3055129132218151</v>
       </c>
       <c r="T86">
-        <v>3.173371776805257</v>
+        <v>3.38492989525894</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.04352196381597443</v>
+        <v>0.04300994071225708</v>
       </c>
       <c r="W86">
-        <v>0.2255375209321933</v>
+        <v>0.2256582559800498</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.13600613692492</v>
+        <v>0.1344060647258034</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2376364545663146</v>
+        <v>0.2395364545663146</v>
       </c>
       <c r="C87">
-        <v>-773.2628491516681</v>
+        <v>-788.0545261135583</v>
       </c>
       <c r="D87">
-        <v>252.7421508483319</v>
+        <v>250.2634738864417</v>
       </c>
       <c r="E87">
-        <v>861.105</v>
+        <v>873.4179999999999</v>
       </c>
       <c r="F87">
-        <v>1046.605</v>
+        <v>1058.918</v>
       </c>
       <c r="G87">
         <v>20.6</v>
@@ -8552,37 +8552,37 @@
         <v>33.17</v>
       </c>
       <c r="M87">
-        <v>246.789459</v>
+        <v>249.6928644</v>
       </c>
       <c r="N87">
-        <v>-213.619459</v>
+        <v>-216.5228644</v>
       </c>
       <c r="O87">
-        <v>-68.35822688</v>
+        <v>-69.287316608</v>
       </c>
       <c r="P87">
-        <v>-145.26123212</v>
+        <v>-147.235547792</v>
       </c>
       <c r="Q87">
-        <v>-139.53123212</v>
+        <v>-141.505547792</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3055129132218151</v>
+        <v>0.3240638355948018</v>
       </c>
       <c r="T87">
-        <v>3.38492989525894</v>
+        <v>3.62671060206315</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04300994071225708</v>
+        <v>0.04250982512257968</v>
       </c>
       <c r="W87">
-        <v>0.2256582559800498</v>
+        <v>0.2257761832360957</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1344060647258034</v>
+        <v>0.1328432035080614</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2395364545663146</v>
+        <v>0.2414364545663146</v>
       </c>
       <c r="C88">
-        <v>-788.0545261135583</v>
+        <v>-802.7980577925255</v>
       </c>
       <c r="D88">
-        <v>250.2634738864417</v>
+        <v>247.8329422074745</v>
       </c>
       <c r="E88">
-        <v>873.4179999999999</v>
+        <v>885.731</v>
       </c>
       <c r="F88">
-        <v>1058.918</v>
+        <v>1071.231</v>
       </c>
       <c r="G88">
         <v>20.6</v>
@@ -8634,37 +8634,37 @@
         <v>33.17</v>
       </c>
       <c r="M88">
-        <v>249.6928644</v>
+        <v>252.5962698</v>
       </c>
       <c r="N88">
-        <v>-216.5228644</v>
+        <v>-219.4262698</v>
       </c>
       <c r="O88">
-        <v>-69.287316608</v>
+        <v>-70.21640633600001</v>
       </c>
       <c r="P88">
-        <v>-147.235547792</v>
+        <v>-149.209863464</v>
       </c>
       <c r="Q88">
-        <v>-141.505547792</v>
+        <v>-143.479863464</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3240638355948018</v>
+        <v>0.3454687460251712</v>
       </c>
       <c r="T88">
-        <v>3.62671060206315</v>
+        <v>3.905688340683392</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.04250982512257968</v>
+        <v>0.04202120644300979</v>
       </c>
       <c r="W88">
-        <v>0.2257761832360957</v>
+        <v>0.2258913995207383</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1328432035080614</v>
+        <v>0.1313162701344056</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2414364545663146</v>
+        <v>0.2433364545663146</v>
       </c>
       <c r="C89">
-        <v>-802.7980577925255</v>
+        <v>-817.4948334415722</v>
       </c>
       <c r="D89">
-        <v>247.8329422074745</v>
+        <v>245.4491665584278</v>
       </c>
       <c r="E89">
-        <v>885.731</v>
+        <v>898.0439999999999</v>
       </c>
       <c r="F89">
-        <v>1071.231</v>
+        <v>1083.544</v>
       </c>
       <c r="G89">
         <v>20.6</v>
@@ -8716,37 +8716,37 @@
         <v>33.17</v>
       </c>
       <c r="M89">
-        <v>252.5962698</v>
+        <v>255.4996752</v>
       </c>
       <c r="N89">
-        <v>-219.4262698</v>
+        <v>-222.3296752</v>
       </c>
       <c r="O89">
-        <v>-70.21640633600001</v>
+        <v>-71.145496064</v>
       </c>
       <c r="P89">
-        <v>-149.209863464</v>
+        <v>-151.184179136</v>
       </c>
       <c r="Q89">
-        <v>-143.479863464</v>
+        <v>-145.454179136</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3454687460251712</v>
+        <v>0.3704411415272689</v>
       </c>
       <c r="T89">
-        <v>3.905688340683392</v>
+        <v>4.231162369073676</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.04202120644300979</v>
+        <v>0.04154369273343014</v>
       </c>
       <c r="W89">
-        <v>0.2258913995207383</v>
+        <v>0.2260039972534572</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1313162701344056</v>
+        <v>0.1298240397919691</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2433364545663146</v>
+        <v>0.2452364545663146</v>
       </c>
       <c r="C90">
-        <v>-817.4948334415722</v>
+        <v>-832.1461893729145</v>
       </c>
       <c r="D90">
-        <v>245.4491665584278</v>
+        <v>243.1108106270856</v>
       </c>
       <c r="E90">
-        <v>898.0439999999999</v>
+        <v>910.357</v>
       </c>
       <c r="F90">
-        <v>1083.544</v>
+        <v>1095.857</v>
       </c>
       <c r="G90">
         <v>20.6</v>
@@ -8798,37 +8798,37 @@
         <v>33.17</v>
       </c>
       <c r="M90">
-        <v>255.4996752</v>
+        <v>258.4030806</v>
       </c>
       <c r="N90">
-        <v>-222.3296752</v>
+        <v>-225.2330806</v>
       </c>
       <c r="O90">
-        <v>-71.145496064</v>
+        <v>-72.07458579199999</v>
       </c>
       <c r="P90">
-        <v>-151.184179136</v>
+        <v>-153.158494808</v>
       </c>
       <c r="Q90">
-        <v>-145.454179136</v>
+        <v>-147.428494808</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3704411415272689</v>
+        <v>0.3999539725752024</v>
       </c>
       <c r="T90">
-        <v>4.231162369073676</v>
+        <v>4.615813493534919</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.04154369273343014</v>
+        <v>0.04107690966900957</v>
       </c>
       <c r="W90">
-        <v>0.2260039972534572</v>
+        <v>0.2261140647000476</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1298240397919691</v>
+        <v>0.1283653427156549</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2452364545663146</v>
+        <v>0.2471364545663146</v>
       </c>
       <c r="C91">
-        <v>-832.1461893729145</v>
+        <v>-846.7534114559767</v>
       </c>
       <c r="D91">
-        <v>243.1108106270856</v>
+        <v>240.8165885440235</v>
       </c>
       <c r="E91">
-        <v>910.357</v>
+        <v>922.6700000000001</v>
       </c>
       <c r="F91">
-        <v>1095.857</v>
+        <v>1108.17</v>
       </c>
       <c r="G91">
         <v>20.6</v>
@@ -8880,37 +8880,37 @@
         <v>33.17</v>
       </c>
       <c r="M91">
-        <v>258.4030806</v>
+        <v>261.306486</v>
       </c>
       <c r="N91">
-        <v>-225.2330806</v>
+        <v>-228.136486</v>
       </c>
       <c r="O91">
-        <v>-72.07458579199999</v>
+        <v>-73.00367552</v>
       </c>
       <c r="P91">
-        <v>-153.158494808</v>
+        <v>-155.13281048</v>
       </c>
       <c r="Q91">
-        <v>-147.428494808</v>
+        <v>-149.40281048</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3999539725752024</v>
+        <v>0.4353693698327227</v>
       </c>
       <c r="T91">
-        <v>4.615813493534919</v>
+        <v>5.077394842888412</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.04107690966900957</v>
+        <v>0.04062049956157614</v>
       </c>
       <c r="W91">
-        <v>0.2261140647000476</v>
+        <v>0.2262216862033804</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1283653427156549</v>
+        <v>0.1269390611299255</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2471364545663146</v>
+        <v>0.2490364545663146</v>
       </c>
       <c r="C92">
-        <v>-846.7534114559767</v>
+        <v>-861.3177374752677</v>
       </c>
       <c r="D92">
-        <v>240.8165885440235</v>
+        <v>238.5652625247323</v>
       </c>
       <c r="E92">
-        <v>922.6700000000001</v>
+        <v>934.9829999999999</v>
       </c>
       <c r="F92">
-        <v>1108.17</v>
+        <v>1120.483</v>
       </c>
       <c r="G92">
         <v>20.6</v>
@@ -8962,37 +8962,37 @@
         <v>33.17</v>
       </c>
       <c r="M92">
-        <v>261.306486</v>
+        <v>264.2098914</v>
       </c>
       <c r="N92">
-        <v>-228.136486</v>
+        <v>-231.0398914</v>
       </c>
       <c r="O92">
-        <v>-73.00367552</v>
+        <v>-73.932765248</v>
       </c>
       <c r="P92">
-        <v>-155.13281048</v>
+        <v>-157.107126152</v>
       </c>
       <c r="Q92">
-        <v>-149.40281048</v>
+        <v>-151.377126152</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4353693698327227</v>
+        <v>0.4786548553696919</v>
       </c>
       <c r="T92">
-        <v>5.077394842888412</v>
+        <v>5.641549825431569</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.04062049956157614</v>
+        <v>0.04017412044551486</v>
       </c>
       <c r="W92">
-        <v>0.2262216862033804</v>
+        <v>0.2263269423989476</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1269390611299255</v>
+        <v>0.125544126392234</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2490364545663146</v>
+        <v>0.2509364545663146</v>
       </c>
       <c r="C93">
-        <v>-861.3177374752677</v>
+        <v>-875.8403593572257</v>
       </c>
       <c r="D93">
-        <v>238.5652625247323</v>
+        <v>236.3556406427743</v>
       </c>
       <c r="E93">
-        <v>934.9829999999999</v>
+        <v>947.296</v>
       </c>
       <c r="F93">
-        <v>1120.483</v>
+        <v>1132.796</v>
       </c>
       <c r="G93">
         <v>20.6</v>
@@ -9044,37 +9044,37 @@
         <v>33.17</v>
       </c>
       <c r="M93">
-        <v>264.2098914</v>
+        <v>267.1132968</v>
       </c>
       <c r="N93">
-        <v>-231.0398914</v>
+        <v>-233.9432968</v>
       </c>
       <c r="O93">
-        <v>-73.932765248</v>
+        <v>-74.861854976</v>
       </c>
       <c r="P93">
-        <v>-157.107126152</v>
+        <v>-159.081441824</v>
       </c>
       <c r="Q93">
-        <v>-151.377126152</v>
+        <v>-153.351441824</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4786548553696919</v>
+        <v>0.5327617122909035</v>
       </c>
       <c r="T93">
-        <v>5.641549825431569</v>
+        <v>6.346743553610517</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04017412044551486</v>
+        <v>0.039737445223281</v>
       </c>
       <c r="W93">
-        <v>0.2263269423989476</v>
+        <v>0.2264299104163503</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.125544126392234</v>
+        <v>0.1241795163227531</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2509364545663146</v>
+        <v>0.2528364545663145</v>
       </c>
       <c r="C94">
-        <v>-875.8403593572257</v>
+        <v>-890.3224252744426</v>
       </c>
       <c r="D94">
-        <v>236.3556406427743</v>
+        <v>234.1865747255573</v>
       </c>
       <c r="E94">
-        <v>947.296</v>
+        <v>959.6089999999999</v>
       </c>
       <c r="F94">
-        <v>1132.796</v>
+        <v>1145.109</v>
       </c>
       <c r="G94">
         <v>20.6</v>
@@ -9126,37 +9126,37 @@
         <v>33.17</v>
       </c>
       <c r="M94">
-        <v>267.1132968</v>
+        <v>270.0167022</v>
       </c>
       <c r="N94">
-        <v>-233.9432968</v>
+        <v>-236.8467022</v>
       </c>
       <c r="O94">
-        <v>-74.861854976</v>
+        <v>-75.790944704</v>
       </c>
       <c r="P94">
-        <v>-159.081441824</v>
+        <v>-161.055757496</v>
       </c>
       <c r="Q94">
-        <v>-153.351441824</v>
+        <v>-155.325757496</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5327617122909035</v>
+        <v>0.6023276711896041</v>
       </c>
       <c r="T94">
-        <v>6.346743553610517</v>
+        <v>7.253421204126306</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.039737445223281</v>
+        <v>0.03931016086604142</v>
       </c>
       <c r="W94">
-        <v>0.2264299104163503</v>
+        <v>0.2265306640677874</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1241795163227531</v>
+        <v>0.1228442527063794</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2528364545663145</v>
+        <v>0.2547364545663146</v>
       </c>
       <c r="C95">
-        <v>-890.3224252744426</v>
+        <v>-904.765041635083</v>
       </c>
       <c r="D95">
-        <v>234.1865747255573</v>
+        <v>232.0569583649171</v>
       </c>
       <c r="E95">
-        <v>959.6089999999999</v>
+        <v>971.922</v>
       </c>
       <c r="F95">
-        <v>1145.109</v>
+        <v>1157.422</v>
       </c>
       <c r="G95">
         <v>20.6</v>
@@ -9208,37 +9208,37 @@
         <v>33.17</v>
       </c>
       <c r="M95">
-        <v>270.0167022</v>
+        <v>272.9201076</v>
       </c>
       <c r="N95">
-        <v>-236.8467022</v>
+        <v>-239.7501076</v>
       </c>
       <c r="O95">
-        <v>-75.790944704</v>
+        <v>-76.72003443199999</v>
       </c>
       <c r="P95">
-        <v>-161.055757496</v>
+        <v>-163.030073168</v>
       </c>
       <c r="Q95">
-        <v>-155.325757496</v>
+        <v>-157.300073168</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6023276711896041</v>
+        <v>0.6950822830545382</v>
       </c>
       <c r="T95">
-        <v>7.253421204126306</v>
+        <v>8.462324738147359</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03931016086604142</v>
+        <v>0.03889196766533885</v>
       </c>
       <c r="W95">
-        <v>0.2265306640677874</v>
+        <v>0.2266292740245131</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1228442527063794</v>
+        <v>0.1215373989541839</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2547364545663146</v>
+        <v>0.2566364545663146</v>
       </c>
       <c r="C96">
-        <v>-904.765041635083</v>
+        <v>-919.1692749647284</v>
       </c>
       <c r="D96">
-        <v>232.0569583649171</v>
+        <v>229.9657250352717</v>
       </c>
       <c r="E96">
-        <v>971.922</v>
+        <v>984.2350000000001</v>
       </c>
       <c r="F96">
-        <v>1157.422</v>
+        <v>1169.735</v>
       </c>
       <c r="G96">
         <v>20.6</v>
@@ -9290,37 +9290,37 @@
         <v>33.17</v>
       </c>
       <c r="M96">
-        <v>272.9201076</v>
+        <v>275.823513</v>
       </c>
       <c r="N96">
-        <v>-239.7501076</v>
+        <v>-242.653513</v>
       </c>
       <c r="O96">
-        <v>-76.72003443199999</v>
+        <v>-77.64912416000001</v>
       </c>
       <c r="P96">
-        <v>-163.030073168</v>
+        <v>-165.00438884</v>
       </c>
       <c r="Q96">
-        <v>-157.300073168</v>
+        <v>-159.27438884</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6950822830545382</v>
+        <v>0.8249387396654462</v>
       </c>
       <c r="T96">
-        <v>8.462324738147359</v>
+        <v>10.15478968577684</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03889196766533885</v>
+        <v>0.03848257853201949</v>
       </c>
       <c r="W96">
-        <v>0.2266292740245131</v>
+        <v>0.2267258079821498</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1215373989541839</v>
+        <v>0.1202580579125609</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2566364545663146</v>
+        <v>0.2585364545663146</v>
       </c>
       <c r="C97">
-        <v>-919.1692749647284</v>
+        <v>-933.5361536873843</v>
       </c>
       <c r="D97">
-        <v>229.9657250352717</v>
+        <v>227.9118463126158</v>
       </c>
       <c r="E97">
-        <v>984.2350000000001</v>
+        <v>996.548</v>
       </c>
       <c r="F97">
-        <v>1169.735</v>
+        <v>1182.048</v>
       </c>
       <c r="G97">
         <v>20.6</v>
@@ -9372,37 +9372,37 @@
         <v>33.17</v>
       </c>
       <c r="M97">
-        <v>275.823513</v>
+        <v>278.7269184</v>
       </c>
       <c r="N97">
-        <v>-242.653513</v>
+        <v>-245.5569184</v>
       </c>
       <c r="O97">
-        <v>-77.64912416000001</v>
+        <v>-78.57821388799999</v>
       </c>
       <c r="P97">
-        <v>-165.00438884</v>
+        <v>-166.978704512</v>
       </c>
       <c r="Q97">
-        <v>-159.27438884</v>
+        <v>-161.248704512</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8249387396654462</v>
+        <v>1.019723424581808</v>
       </c>
       <c r="T97">
-        <v>10.15478968577684</v>
+        <v>12.69348710722105</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03848257853201949</v>
+        <v>0.03808171833897763</v>
       </c>
       <c r="W97">
-        <v>0.2267258079821498</v>
+        <v>0.2268203308156691</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1202580579125609</v>
+        <v>0.1190053698093051</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2585364545663146</v>
+        <v>0.2604364545663146</v>
       </c>
       <c r="C98">
-        <v>-933.5361536873843</v>
+        <v>-947.8666698118884</v>
       </c>
       <c r="D98">
-        <v>227.9118463126158</v>
+        <v>225.8943301881115</v>
       </c>
       <c r="E98">
-        <v>996.548</v>
+        <v>1008.861</v>
       </c>
       <c r="F98">
-        <v>1182.048</v>
+        <v>1194.361</v>
       </c>
       <c r="G98">
         <v>20.6</v>
@@ -9454,37 +9454,37 @@
         <v>33.17</v>
       </c>
       <c r="M98">
-        <v>278.7269184</v>
+        <v>281.6303238</v>
       </c>
       <c r="N98">
-        <v>-245.5569184</v>
+        <v>-248.4603238</v>
       </c>
       <c r="O98">
-        <v>-78.57821388799999</v>
+        <v>-79.50730361599999</v>
       </c>
       <c r="P98">
-        <v>-166.978704512</v>
+        <v>-168.953020184</v>
       </c>
       <c r="Q98">
-        <v>-161.248704512</v>
+        <v>-163.223020184</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.019723424581806</v>
+        <v>1.344364566109074</v>
       </c>
       <c r="T98">
-        <v>12.69348710722102</v>
+        <v>16.92464947629469</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03808171833897763</v>
+        <v>0.03768912330455518</v>
       </c>
       <c r="W98">
-        <v>0.2268203308156691</v>
+        <v>0.2269129047247859</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1190053698093051</v>
+        <v>0.117778510326735</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2604364545663146</v>
+        <v>0.2623364545663146</v>
       </c>
       <c r="C99">
-        <v>-947.8666698118884</v>
+        <v>-962.1617805295366</v>
       </c>
       <c r="D99">
-        <v>225.8943301881115</v>
+        <v>223.9122194704634</v>
       </c>
       <c r="E99">
-        <v>1008.861</v>
+        <v>1021.174</v>
       </c>
       <c r="F99">
-        <v>1194.361</v>
+        <v>1206.674</v>
       </c>
       <c r="G99">
         <v>20.6</v>
@@ -9536,37 +9536,37 @@
         <v>33.17</v>
       </c>
       <c r="M99">
-        <v>281.6303238</v>
+        <v>284.5337292</v>
       </c>
       <c r="N99">
-        <v>-248.4603238</v>
+        <v>-251.3637292</v>
       </c>
       <c r="O99">
-        <v>-79.50730361599999</v>
+        <v>-80.436393344</v>
       </c>
       <c r="P99">
-        <v>-168.953020184</v>
+        <v>-170.927335856</v>
       </c>
       <c r="Q99">
-        <v>-163.223020184</v>
+        <v>-165.197335856</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.344364566109074</v>
+        <v>1.993646849163612</v>
       </c>
       <c r="T99">
-        <v>16.92464947629469</v>
+        <v>25.38697421444203</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03768912330455518</v>
+        <v>0.03730454041369238</v>
       </c>
       <c r="W99">
-        <v>0.2269129047247859</v>
+        <v>0.2270035893704513</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.117778510326735</v>
+        <v>0.1165766887927887</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2623364545663146</v>
+        <v>0.2642364545663146</v>
       </c>
       <c r="C100">
-        <v>-962.1617805295366</v>
+        <v>-976.422409728328</v>
       </c>
       <c r="D100">
-        <v>223.9122194704634</v>
+        <v>221.9645902716719</v>
       </c>
       <c r="E100">
-        <v>1021.174</v>
+        <v>1033.487</v>
       </c>
       <c r="F100">
-        <v>1206.674</v>
+        <v>1218.987</v>
       </c>
       <c r="G100">
         <v>20.6</v>
@@ -9618,37 +9618,37 @@
         <v>33.17</v>
       </c>
       <c r="M100">
-        <v>284.5337292</v>
+        <v>287.4371346</v>
       </c>
       <c r="N100">
-        <v>-251.3637292</v>
+        <v>-254.2671346</v>
       </c>
       <c r="O100">
-        <v>-80.436393344</v>
+        <v>-81.36548307199999</v>
       </c>
       <c r="P100">
-        <v>-170.927335856</v>
+        <v>-172.901651528</v>
       </c>
       <c r="Q100">
-        <v>-165.197335856</v>
+        <v>-167.171651528</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.993646849163612</v>
+        <v>3.941493698327222</v>
       </c>
       <c r="T100">
-        <v>25.38697421444203</v>
+        <v>50.77394842888406</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03730454041369238</v>
+        <v>0.03692772687416013</v>
       </c>
       <c r="W100">
-        <v>0.2270035893704513</v>
+        <v>0.227092442003073</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1165766887927887</v>
+        <v>0.1153991464817504</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2642364545663146</v>
-      </c>
-      <c r="C101">
-        <v>-976.422409728328</v>
-      </c>
-      <c r="D101">
-        <v>221.9645902716719</v>
-      </c>
-      <c r="E101">
-        <v>1033.487</v>
-      </c>
-      <c r="F101">
-        <v>1218.987</v>
-      </c>
-      <c r="G101">
-        <v>20.6</v>
-      </c>
-      <c r="H101">
-        <v>1045.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>38.9</v>
-      </c>
-      <c r="K101">
-        <v>5.73</v>
-      </c>
-      <c r="L101">
-        <v>33.17</v>
-      </c>
-      <c r="M101">
-        <v>287.4371346</v>
-      </c>
-      <c r="N101">
-        <v>-254.2671346</v>
-      </c>
-      <c r="O101">
-        <v>-81.36548307199999</v>
-      </c>
-      <c r="P101">
-        <v>-172.901651528</v>
-      </c>
-      <c r="Q101">
-        <v>-167.171651528</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.941493698327222</v>
-      </c>
-      <c r="T101">
-        <v>50.77394842888406</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03692772687416013</v>
-      </c>
-      <c r="W101">
-        <v>0.227092442003073</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1153991464817504</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
